--- a/server/src/main/resources/templates/trade_template.xlsx
+++ b/server/src/main/resources/templates/trade_template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr codeName="현재_통합_문서" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\소장공유\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qaz25\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F8152A-1843-46BE-8B93-E6FD751B0A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12870" tabRatio="831"/>
+    <workbookView xWindow="38280" yWindow="-60" windowWidth="38640" windowHeight="21120" tabRatio="831" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="빈문서" sheetId="114" r:id="rId1"/>
@@ -17,10 +18,21 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">빈문서!$B$1:$AF$49</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -224,7 +236,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="11">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="yyyy\ &quot;년&quot;\ mm\ &quot;월&quot;\ dd\ &quot;일&quot;\(aaa\)"/>
@@ -238,7 +250,7 @@
     <numFmt numFmtId="184" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="185" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -445,6 +457,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF002060"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -845,7 +866,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -861,7 +882,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -870,13 +891,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -945,13 +966,7 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -969,318 +984,318 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="9" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="15" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="16" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="20" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="16" fillId="2" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="23" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="184" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="184" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="185" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="23" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="16" fillId="2" borderId="7" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="6" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="쉼표 [0] 2" xfId="4"/>
+    <cellStyle name="쉼표 [0] 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="3"/>
-    <cellStyle name="표준_200609_거래명세서_외부" xfId="1"/>
+    <cellStyle name="표준 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="표준_200609_거래명세서_외부" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1307,19 +1322,25 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>347602</xdr:colOff>
+      <xdr:colOff>241789</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>287863</xdr:rowOff>
+      <xdr:rowOff>280536</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>200352</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>17180</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>122546</xdr:rowOff>
+      <xdr:rowOff>115219</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 1"/>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1339,8 +1360,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="9263002" y="2926288"/>
-          <a:ext cx="805250" cy="806233"/>
+          <a:off x="9136674" y="2918228"/>
+          <a:ext cx="962352" cy="801837"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1389,12 +1410,18 @@
         </xdr:to>
         <xdr:pic>
           <xdr:nvPicPr>
-            <xdr:cNvPr id="3" name="그림 2"/>
+            <xdr:cNvPr id="3" name="그림 2">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
             <xdr:cNvPicPr>
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="#REF!" spid="_x0000_s1197059"/>
+                  <a14:cameraTool cellRange="#REF!" spid="_x0000_s1197060"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1451,7 +1478,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3"/>
+        <xdr:cNvPr id="4" name="그림 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1506,7 +1539,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 18"/>
+        <xdr:cNvPr id="5" name="Picture 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -1552,7 +1591,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="그림 5"/>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1846,7 +1891,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1869,242 +1914,242 @@
       <c r="AP1" s="30"/>
     </row>
     <row r="2" spans="2:42" ht="85.5" customHeight="1">
-      <c r="B2" s="130" t="s">
+      <c r="B2" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="131"/>
-      <c r="D2" s="131"/>
-      <c r="E2" s="131"/>
-      <c r="F2" s="131"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="131"/>
-      <c r="L2" s="131"/>
-      <c r="M2" s="131"/>
-      <c r="N2" s="131"/>
-      <c r="O2" s="131"/>
-      <c r="P2" s="131"/>
-      <c r="Q2" s="131"/>
-      <c r="R2" s="131"/>
-      <c r="S2" s="131"/>
-      <c r="T2" s="131"/>
-      <c r="U2" s="131"/>
-      <c r="V2" s="131"/>
-      <c r="W2" s="131"/>
-      <c r="X2" s="131"/>
-      <c r="Y2" s="131"/>
-      <c r="Z2" s="131"/>
-      <c r="AA2" s="131"/>
-      <c r="AB2" s="131"/>
-      <c r="AC2" s="131"/>
-      <c r="AD2" s="131"/>
-      <c r="AE2" s="131"/>
-      <c r="AF2" s="132"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
+      <c r="AF2" s="41"/>
     </row>
     <row r="3" spans="2:42" ht="38.25" customHeight="1">
       <c r="B3" s="3"/>
-      <c r="C3" s="133"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
-      <c r="I3" s="134"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="122" t="s">
+      <c r="C3" s="42"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="122" t="s">
+      <c r="L3" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="122"/>
-      <c r="N3" s="122"/>
-      <c r="O3" s="122"/>
-      <c r="P3" s="135" t="s">
+      <c r="M3" s="44"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="44"/>
+      <c r="P3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="Q3" s="135"/>
-      <c r="R3" s="135"/>
-      <c r="S3" s="135"/>
-      <c r="T3" s="135"/>
-      <c r="U3" s="135"/>
-      <c r="V3" s="135"/>
-      <c r="W3" s="135"/>
-      <c r="X3" s="135"/>
-      <c r="Y3" s="135"/>
-      <c r="Z3" s="135"/>
-      <c r="AA3" s="135"/>
-      <c r="AB3" s="135"/>
-      <c r="AC3" s="135"/>
-      <c r="AD3" s="135"/>
-      <c r="AE3" s="135"/>
-      <c r="AF3" s="136"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="45"/>
+      <c r="T3" s="45"/>
+      <c r="U3" s="45"/>
+      <c r="V3" s="45"/>
+      <c r="W3" s="45"/>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="45"/>
+      <c r="AA3" s="45"/>
+      <c r="AB3" s="45"/>
+      <c r="AC3" s="45"/>
+      <c r="AD3" s="45"/>
+      <c r="AE3" s="45"/>
+      <c r="AF3" s="46"/>
       <c r="AH3" s="4"/>
       <c r="AI3" s="31"/>
     </row>
     <row r="4" spans="2:42" ht="38.25" customHeight="1">
-      <c r="B4" s="137"/>
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="139"/>
-      <c r="I4" s="140" t="s">
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="J4" s="141"/>
-      <c r="K4" s="122"/>
-      <c r="L4" s="122" t="s">
+      <c r="J4" s="51"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="M4" s="122"/>
-      <c r="N4" s="122"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="142" t="s">
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="Q4" s="142"/>
-      <c r="R4" s="142"/>
-      <c r="S4" s="142"/>
-      <c r="T4" s="142"/>
-      <c r="U4" s="142"/>
-      <c r="V4" s="142"/>
-      <c r="W4" s="142"/>
-      <c r="X4" s="127" t="s">
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="Y4" s="127"/>
-      <c r="Z4" s="117" t="s">
+      <c r="Y4" s="53"/>
+      <c r="Z4" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="118"/>
-      <c r="AE4" s="118"/>
-      <c r="AF4" s="119"/>
+      <c r="AA4" s="55"/>
+      <c r="AB4" s="55"/>
+      <c r="AC4" s="55"/>
+      <c r="AD4" s="55"/>
+      <c r="AE4" s="55"/>
+      <c r="AF4" s="56"/>
       <c r="AH4" s="4"/>
       <c r="AI4" s="32"/>
     </row>
     <row r="5" spans="2:42" ht="38.25" customHeight="1">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="121"/>
-      <c r="D5" s="121"/>
-      <c r="E5" s="121"/>
-      <c r="F5" s="121"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="121"/>
-      <c r="K5" s="122"/>
-      <c r="L5" s="122" t="s">
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="M5" s="122"/>
-      <c r="N5" s="122"/>
-      <c r="O5" s="122"/>
-      <c r="P5" s="123" t="s">
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="Q5" s="123"/>
-      <c r="R5" s="123"/>
-      <c r="S5" s="123"/>
-      <c r="T5" s="123"/>
-      <c r="U5" s="123"/>
-      <c r="V5" s="123"/>
-      <c r="W5" s="123"/>
-      <c r="X5" s="123"/>
-      <c r="Y5" s="123"/>
-      <c r="Z5" s="123"/>
-      <c r="AA5" s="123"/>
-      <c r="AB5" s="123"/>
-      <c r="AC5" s="123"/>
-      <c r="AD5" s="123"/>
-      <c r="AE5" s="123"/>
-      <c r="AF5" s="124"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="59"/>
+      <c r="T5" s="59"/>
+      <c r="U5" s="59"/>
+      <c r="V5" s="59"/>
+      <c r="W5" s="59"/>
+      <c r="X5" s="59"/>
+      <c r="Y5" s="59"/>
+      <c r="Z5" s="59"/>
+      <c r="AA5" s="59"/>
+      <c r="AB5" s="59"/>
+      <c r="AC5" s="59"/>
+      <c r="AD5" s="59"/>
+      <c r="AE5" s="59"/>
+      <c r="AF5" s="60"/>
     </row>
     <row r="6" spans="2:42" ht="38.25" customHeight="1">
-      <c r="B6" s="125">
+      <c r="B6" s="61">
         <f>Q28</f>
         <v>0</v>
       </c>
-      <c r="C6" s="126"/>
-      <c r="D6" s="126"/>
-      <c r="E6" s="126"/>
-      <c r="F6" s="126"/>
-      <c r="G6" s="126"/>
-      <c r="H6" s="126"/>
-      <c r="I6" s="126"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="122"/>
-      <c r="L6" s="122" t="s">
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
+      <c r="G6" s="62"/>
+      <c r="H6" s="62"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="62"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="122"/>
-      <c r="N6" s="122"/>
-      <c r="O6" s="122"/>
-      <c r="P6" s="123" t="s">
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="Q6" s="123"/>
-      <c r="R6" s="123"/>
-      <c r="S6" s="123"/>
-      <c r="T6" s="123"/>
-      <c r="U6" s="123"/>
-      <c r="V6" s="127" t="s">
+      <c r="Q6" s="59"/>
+      <c r="R6" s="59"/>
+      <c r="S6" s="59"/>
+      <c r="T6" s="59"/>
+      <c r="U6" s="59"/>
+      <c r="V6" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="W6" s="127"/>
-      <c r="X6" s="123" t="s">
+      <c r="W6" s="53"/>
+      <c r="X6" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="Y6" s="123"/>
-      <c r="Z6" s="128"/>
-      <c r="AA6" s="128"/>
-      <c r="AB6" s="128"/>
-      <c r="AC6" s="128"/>
-      <c r="AD6" s="128"/>
-      <c r="AE6" s="128"/>
-      <c r="AF6" s="129"/>
+      <c r="Y6" s="59"/>
+      <c r="Z6" s="63"/>
+      <c r="AA6" s="63"/>
+      <c r="AB6" s="63"/>
+      <c r="AC6" s="63"/>
+      <c r="AD6" s="63"/>
+      <c r="AE6" s="63"/>
+      <c r="AF6" s="64"/>
     </row>
     <row r="7" spans="2:42" s="7" customFormat="1" ht="43.5" customHeight="1">
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="65" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
       <c r="F7" s="5"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="112"/>
-      <c r="I7" s="112"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="112"/>
-      <c r="L7" s="112"/>
-      <c r="M7" s="112"/>
-      <c r="N7" s="112"/>
-      <c r="O7" s="112"/>
-      <c r="P7" s="112"/>
-      <c r="Q7" s="112"/>
-      <c r="R7" s="112"/>
-      <c r="S7" s="112"/>
-      <c r="T7" s="112"/>
-      <c r="U7" s="112"/>
-      <c r="V7" s="112"/>
-      <c r="W7" s="112"/>
-      <c r="X7" s="112"/>
-      <c r="Y7" s="112"/>
-      <c r="Z7" s="112"/>
-      <c r="AA7" s="112"/>
-      <c r="AB7" s="112"/>
-      <c r="AC7" s="112"/>
-      <c r="AD7" s="112"/>
-      <c r="AE7" s="33"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="68"/>
+      <c r="N7" s="68"/>
+      <c r="O7" s="68"/>
+      <c r="P7" s="68"/>
+      <c r="Q7" s="68"/>
+      <c r="R7" s="68"/>
+      <c r="S7" s="68"/>
+      <c r="T7" s="68"/>
+      <c r="U7" s="68"/>
+      <c r="V7" s="68"/>
+      <c r="W7" s="68"/>
+      <c r="X7" s="68"/>
+      <c r="Y7" s="68"/>
+      <c r="Z7" s="68"/>
+      <c r="AA7" s="68"/>
+      <c r="AB7" s="68"/>
+      <c r="AC7" s="68"/>
+      <c r="AD7" s="68"/>
+      <c r="AE7" s="9"/>
       <c r="AF7" s="6"/>
       <c r="AH7" s="4"/>
       <c r="AI7" s="4"/>
@@ -2115,40 +2160,40 @@
       <c r="AN7" s="4"/>
     </row>
     <row r="8" spans="2:42" s="7" customFormat="1" ht="33" customHeight="1">
-      <c r="B8" s="113" t="s">
+      <c r="B8" s="69" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="114"/>
-      <c r="D8" s="114"/>
-      <c r="E8" s="115"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="71"/>
       <c r="F8" s="8"/>
-      <c r="G8" s="116"/>
-      <c r="H8" s="116"/>
-      <c r="I8" s="116"/>
-      <c r="J8" s="116"/>
-      <c r="K8" s="116"/>
-      <c r="L8" s="116"/>
-      <c r="M8" s="116"/>
-      <c r="N8" s="116"/>
-      <c r="O8" s="116"/>
-      <c r="P8" s="116"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="42"/>
       <c r="Q8" s="9"/>
       <c r="R8" s="10" t="s">
         <v>17</v>
       </c>
       <c r="S8" s="9"/>
-      <c r="T8" s="116"/>
-      <c r="U8" s="116"/>
-      <c r="V8" s="116"/>
-      <c r="W8" s="116"/>
-      <c r="X8" s="116"/>
-      <c r="Y8" s="116"/>
-      <c r="Z8" s="116"/>
-      <c r="AA8" s="116"/>
-      <c r="AB8" s="116"/>
-      <c r="AC8" s="116"/>
-      <c r="AD8" s="116"/>
-      <c r="AE8" s="116"/>
+      <c r="T8" s="42"/>
+      <c r="U8" s="42"/>
+      <c r="V8" s="42"/>
+      <c r="W8" s="42"/>
+      <c r="X8" s="42"/>
+      <c r="Y8" s="42"/>
+      <c r="Z8" s="42"/>
+      <c r="AA8" s="42"/>
+      <c r="AB8" s="42"/>
+      <c r="AC8" s="42"/>
+      <c r="AD8" s="42"/>
+      <c r="AE8" s="42"/>
       <c r="AF8" s="11"/>
       <c r="AH8" s="4"/>
       <c r="AI8" s="4"/>
@@ -2162,95 +2207,95 @@
       <c r="B9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="109" t="s">
+      <c r="D9" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="109"/>
-      <c r="F9" s="109"/>
-      <c r="G9" s="109"/>
-      <c r="H9" s="109"/>
-      <c r="I9" s="109"/>
-      <c r="J9" s="109"/>
-      <c r="K9" s="109" t="s">
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="109"/>
-      <c r="M9" s="109"/>
-      <c r="N9" s="109" t="s">
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="O9" s="109"/>
-      <c r="P9" s="109"/>
-      <c r="Q9" s="109" t="s">
+      <c r="O9" s="72"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="R9" s="109"/>
-      <c r="S9" s="109"/>
-      <c r="T9" s="109" t="s">
+      <c r="R9" s="72"/>
+      <c r="S9" s="72"/>
+      <c r="T9" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="U9" s="109"/>
-      <c r="V9" s="109"/>
-      <c r="W9" s="109"/>
-      <c r="X9" s="109"/>
-      <c r="Y9" s="109"/>
-      <c r="Z9" s="109" t="s">
+      <c r="U9" s="72"/>
+      <c r="V9" s="72"/>
+      <c r="W9" s="72"/>
+      <c r="X9" s="72"/>
+      <c r="Y9" s="72"/>
+      <c r="Z9" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="AA9" s="109"/>
-      <c r="AB9" s="109"/>
-      <c r="AC9" s="109"/>
-      <c r="AD9" s="109"/>
-      <c r="AE9" s="109" t="s">
+      <c r="AA9" s="72"/>
+      <c r="AB9" s="72"/>
+      <c r="AC9" s="72"/>
+      <c r="AD9" s="72"/>
+      <c r="AE9" s="72" t="s">
         <v>26</v>
       </c>
-      <c r="AF9" s="110"/>
+      <c r="AF9" s="73"/>
     </row>
     <row r="10" spans="2:42" s="14" customFormat="1" ht="40.5" customHeight="1">
       <c r="B10" s="13"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="100"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="100"/>
-      <c r="G10" s="100"/>
-      <c r="H10" s="100"/>
-      <c r="I10" s="100"/>
-      <c r="J10" s="100"/>
-      <c r="K10" s="108">
+      <c r="C10" s="36"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="74"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="75">
         <v>0</v>
       </c>
-      <c r="L10" s="108"/>
-      <c r="M10" s="108"/>
-      <c r="N10" s="102">
+      <c r="L10" s="75"/>
+      <c r="M10" s="75"/>
+      <c r="N10" s="76">
         <v>0</v>
       </c>
-      <c r="O10" s="102"/>
-      <c r="P10" s="102"/>
-      <c r="Q10" s="103"/>
-      <c r="R10" s="104"/>
-      <c r="S10" s="105"/>
-      <c r="T10" s="106">
+      <c r="O10" s="76"/>
+      <c r="P10" s="76"/>
+      <c r="Q10" s="77"/>
+      <c r="R10" s="78"/>
+      <c r="S10" s="79"/>
+      <c r="T10" s="80">
         <f>K10*N10*Q10</f>
         <v>0</v>
       </c>
-      <c r="U10" s="106"/>
-      <c r="V10" s="106"/>
-      <c r="W10" s="106"/>
-      <c r="X10" s="106"/>
-      <c r="Y10" s="106"/>
-      <c r="Z10" s="106">
+      <c r="U10" s="80"/>
+      <c r="V10" s="80"/>
+      <c r="W10" s="80"/>
+      <c r="X10" s="80"/>
+      <c r="Y10" s="80"/>
+      <c r="Z10" s="80">
         <f t="shared" ref="Z10:Z21" si="0">T10*10%</f>
         <v>0</v>
       </c>
-      <c r="AA10" s="106"/>
-      <c r="AB10" s="106"/>
-      <c r="AC10" s="106"/>
-      <c r="AD10" s="106"/>
-      <c r="AE10" s="98"/>
-      <c r="AF10" s="99"/>
+      <c r="AA10" s="80"/>
+      <c r="AB10" s="80"/>
+      <c r="AC10" s="80"/>
+      <c r="AD10" s="80"/>
+      <c r="AE10" s="81"/>
+      <c r="AF10" s="82"/>
       <c r="AH10" s="15"/>
       <c r="AI10" s="15"/>
       <c r="AJ10" s="15"/>
@@ -2261,44 +2306,44 @@
     </row>
     <row r="11" spans="2:42" s="14" customFormat="1" ht="40.5" hidden="1" customHeight="1">
       <c r="B11" s="13"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="100" t="s">
+      <c r="C11" s="36"/>
+      <c r="D11" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="100"/>
-      <c r="F11" s="100"/>
-      <c r="G11" s="100"/>
-      <c r="H11" s="100"/>
-      <c r="I11" s="100"/>
-      <c r="J11" s="100"/>
-      <c r="K11" s="108"/>
-      <c r="L11" s="108"/>
-      <c r="M11" s="108"/>
-      <c r="N11" s="102"/>
-      <c r="O11" s="102"/>
-      <c r="P11" s="102"/>
-      <c r="Q11" s="103"/>
-      <c r="R11" s="104"/>
-      <c r="S11" s="105"/>
-      <c r="T11" s="106">
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="74"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="75"/>
+      <c r="M11" s="75"/>
+      <c r="N11" s="76"/>
+      <c r="O11" s="76"/>
+      <c r="P11" s="76"/>
+      <c r="Q11" s="77"/>
+      <c r="R11" s="78"/>
+      <c r="S11" s="79"/>
+      <c r="T11" s="80">
         <f>K11*N11*Q11</f>
         <v>0</v>
       </c>
-      <c r="U11" s="106"/>
-      <c r="V11" s="106"/>
-      <c r="W11" s="106"/>
-      <c r="X11" s="106"/>
-      <c r="Y11" s="106"/>
-      <c r="Z11" s="106">
+      <c r="U11" s="80"/>
+      <c r="V11" s="80"/>
+      <c r="W11" s="80"/>
+      <c r="X11" s="80"/>
+      <c r="Y11" s="80"/>
+      <c r="Z11" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA11" s="106"/>
-      <c r="AB11" s="106"/>
-      <c r="AC11" s="106"/>
-      <c r="AD11" s="106"/>
-      <c r="AE11" s="98"/>
-      <c r="AF11" s="99"/>
+      <c r="AA11" s="80"/>
+      <c r="AB11" s="80"/>
+      <c r="AC11" s="80"/>
+      <c r="AD11" s="80"/>
+      <c r="AE11" s="81"/>
+      <c r="AF11" s="82"/>
       <c r="AH11" s="15"/>
       <c r="AI11" s="16"/>
       <c r="AJ11" s="15"/>
@@ -2309,44 +2354,44 @@
     </row>
     <row r="12" spans="2:42" s="14" customFormat="1" ht="40.5" hidden="1" customHeight="1">
       <c r="B12" s="13"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="100" t="s">
+      <c r="C12" s="36"/>
+      <c r="D12" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="100"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="100"/>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="100"/>
-      <c r="K12" s="108"/>
-      <c r="L12" s="108"/>
-      <c r="M12" s="108"/>
-      <c r="N12" s="102"/>
-      <c r="O12" s="102"/>
-      <c r="P12" s="102"/>
-      <c r="Q12" s="103"/>
-      <c r="R12" s="104"/>
-      <c r="S12" s="105"/>
-      <c r="T12" s="106">
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="75"/>
+      <c r="L12" s="75"/>
+      <c r="M12" s="75"/>
+      <c r="N12" s="76"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="77"/>
+      <c r="R12" s="78"/>
+      <c r="S12" s="79"/>
+      <c r="T12" s="80">
         <f>Q12*N12*K12</f>
         <v>0</v>
       </c>
-      <c r="U12" s="106"/>
-      <c r="V12" s="106"/>
-      <c r="W12" s="106"/>
-      <c r="X12" s="106"/>
-      <c r="Y12" s="106"/>
-      <c r="Z12" s="106">
+      <c r="U12" s="80"/>
+      <c r="V12" s="80"/>
+      <c r="W12" s="80"/>
+      <c r="X12" s="80"/>
+      <c r="Y12" s="80"/>
+      <c r="Z12" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA12" s="106"/>
-      <c r="AB12" s="106"/>
-      <c r="AC12" s="106"/>
-      <c r="AD12" s="106"/>
-      <c r="AE12" s="107"/>
-      <c r="AF12" s="99"/>
+      <c r="AA12" s="80"/>
+      <c r="AB12" s="80"/>
+      <c r="AC12" s="80"/>
+      <c r="AD12" s="80"/>
+      <c r="AE12" s="83"/>
+      <c r="AF12" s="82"/>
       <c r="AH12" s="15"/>
       <c r="AI12" s="16"/>
       <c r="AJ12" s="15"/>
@@ -2357,46 +2402,46 @@
     </row>
     <row r="13" spans="2:42" s="14" customFormat="1" ht="40.5" customHeight="1">
       <c r="B13" s="13"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="100"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="100"/>
-      <c r="G13" s="100"/>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="100"/>
-      <c r="K13" s="108">
+      <c r="C13" s="36"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+      <c r="J13" s="74"/>
+      <c r="K13" s="75">
         <v>0</v>
       </c>
-      <c r="L13" s="108"/>
-      <c r="M13" s="108"/>
-      <c r="N13" s="102">
+      <c r="L13" s="75"/>
+      <c r="M13" s="75"/>
+      <c r="N13" s="76">
         <v>0</v>
       </c>
-      <c r="O13" s="102"/>
-      <c r="P13" s="102"/>
-      <c r="Q13" s="103"/>
-      <c r="R13" s="104"/>
-      <c r="S13" s="105"/>
-      <c r="T13" s="106">
+      <c r="O13" s="76"/>
+      <c r="P13" s="76"/>
+      <c r="Q13" s="77"/>
+      <c r="R13" s="78"/>
+      <c r="S13" s="79"/>
+      <c r="T13" s="80">
         <f>Q13*N13*K13</f>
         <v>0</v>
       </c>
-      <c r="U13" s="106"/>
-      <c r="V13" s="106"/>
-      <c r="W13" s="106"/>
-      <c r="X13" s="106"/>
-      <c r="Y13" s="106"/>
-      <c r="Z13" s="106">
+      <c r="U13" s="80"/>
+      <c r="V13" s="80"/>
+      <c r="W13" s="80"/>
+      <c r="X13" s="80"/>
+      <c r="Y13" s="80"/>
+      <c r="Z13" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA13" s="106"/>
-      <c r="AB13" s="106"/>
-      <c r="AC13" s="106"/>
-      <c r="AD13" s="106"/>
-      <c r="AE13" s="107"/>
-      <c r="AF13" s="99"/>
+      <c r="AA13" s="80"/>
+      <c r="AB13" s="80"/>
+      <c r="AC13" s="80"/>
+      <c r="AD13" s="80"/>
+      <c r="AE13" s="83"/>
+      <c r="AF13" s="82"/>
       <c r="AH13" s="15"/>
       <c r="AI13" s="16"/>
       <c r="AJ13" s="15"/>
@@ -2407,44 +2452,44 @@
     </row>
     <row r="14" spans="2:42" s="14" customFormat="1" ht="40.5" hidden="1" customHeight="1">
       <c r="B14" s="13"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="100" t="s">
+      <c r="C14" s="36"/>
+      <c r="D14" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="100"/>
-      <c r="F14" s="100"/>
-      <c r="G14" s="100"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="100"/>
-      <c r="J14" s="100"/>
-      <c r="K14" s="101"/>
-      <c r="L14" s="101"/>
-      <c r="M14" s="101"/>
-      <c r="N14" s="102"/>
-      <c r="O14" s="102"/>
-      <c r="P14" s="102"/>
-      <c r="Q14" s="103"/>
-      <c r="R14" s="104"/>
-      <c r="S14" s="105"/>
-      <c r="T14" s="97">
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="74"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84"/>
+      <c r="N14" s="76"/>
+      <c r="O14" s="76"/>
+      <c r="P14" s="76"/>
+      <c r="Q14" s="77"/>
+      <c r="R14" s="78"/>
+      <c r="S14" s="79"/>
+      <c r="T14" s="85">
         <f>K14*N14*Q14</f>
         <v>0</v>
       </c>
-      <c r="U14" s="97"/>
-      <c r="V14" s="97"/>
-      <c r="W14" s="97"/>
-      <c r="X14" s="97"/>
-      <c r="Y14" s="97"/>
-      <c r="Z14" s="97">
+      <c r="U14" s="85"/>
+      <c r="V14" s="85"/>
+      <c r="W14" s="85"/>
+      <c r="X14" s="85"/>
+      <c r="Y14" s="85"/>
+      <c r="Z14" s="85">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA14" s="97"/>
-      <c r="AB14" s="97"/>
-      <c r="AC14" s="97"/>
-      <c r="AD14" s="97"/>
-      <c r="AE14" s="89"/>
-      <c r="AF14" s="90"/>
+      <c r="AA14" s="85"/>
+      <c r="AB14" s="85"/>
+      <c r="AC14" s="85"/>
+      <c r="AD14" s="85"/>
+      <c r="AE14" s="86"/>
+      <c r="AF14" s="87"/>
       <c r="AH14" s="15"/>
       <c r="AI14" s="16"/>
       <c r="AJ14" s="15"/>
@@ -2455,44 +2500,44 @@
     </row>
     <row r="15" spans="2:42" s="14" customFormat="1" ht="40.5" hidden="1" customHeight="1">
       <c r="B15" s="13"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="100" t="s">
+      <c r="C15" s="36"/>
+      <c r="D15" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="100"/>
-      <c r="F15" s="100"/>
-      <c r="G15" s="100"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="100"/>
-      <c r="K15" s="101"/>
-      <c r="L15" s="101"/>
-      <c r="M15" s="101"/>
-      <c r="N15" s="102"/>
-      <c r="O15" s="102"/>
-      <c r="P15" s="102"/>
-      <c r="Q15" s="103"/>
-      <c r="R15" s="104"/>
-      <c r="S15" s="105"/>
-      <c r="T15" s="97">
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="74"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="76"/>
+      <c r="P15" s="76"/>
+      <c r="Q15" s="77"/>
+      <c r="R15" s="78"/>
+      <c r="S15" s="79"/>
+      <c r="T15" s="85">
         <f>K15*N15*Q15</f>
         <v>0</v>
       </c>
-      <c r="U15" s="97"/>
-      <c r="V15" s="97"/>
-      <c r="W15" s="97"/>
-      <c r="X15" s="97"/>
-      <c r="Y15" s="97"/>
-      <c r="Z15" s="97">
+      <c r="U15" s="85"/>
+      <c r="V15" s="85"/>
+      <c r="W15" s="85"/>
+      <c r="X15" s="85"/>
+      <c r="Y15" s="85"/>
+      <c r="Z15" s="85">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA15" s="97"/>
-      <c r="AB15" s="97"/>
-      <c r="AC15" s="97"/>
-      <c r="AD15" s="97"/>
-      <c r="AE15" s="89"/>
-      <c r="AF15" s="90"/>
+      <c r="AA15" s="85"/>
+      <c r="AB15" s="85"/>
+      <c r="AC15" s="85"/>
+      <c r="AD15" s="85"/>
+      <c r="AE15" s="86"/>
+      <c r="AF15" s="87"/>
       <c r="AH15" s="15"/>
       <c r="AI15" s="16"/>
       <c r="AJ15" s="15"/>
@@ -2503,44 +2548,44 @@
     </row>
     <row r="16" spans="2:42" s="14" customFormat="1" ht="40.5" hidden="1" customHeight="1">
       <c r="B16" s="13"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="100" t="s">
+      <c r="C16" s="36"/>
+      <c r="D16" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="100"/>
-      <c r="F16" s="100"/>
-      <c r="G16" s="100"/>
-      <c r="H16" s="100"/>
-      <c r="I16" s="100"/>
-      <c r="J16" s="100"/>
-      <c r="K16" s="101"/>
-      <c r="L16" s="101"/>
-      <c r="M16" s="101"/>
-      <c r="N16" s="102"/>
-      <c r="O16" s="102"/>
-      <c r="P16" s="102"/>
-      <c r="Q16" s="103"/>
-      <c r="R16" s="104"/>
-      <c r="S16" s="105"/>
-      <c r="T16" s="106">
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="74"/>
+      <c r="K16" s="84"/>
+      <c r="L16" s="84"/>
+      <c r="M16" s="84"/>
+      <c r="N16" s="76"/>
+      <c r="O16" s="76"/>
+      <c r="P16" s="76"/>
+      <c r="Q16" s="77"/>
+      <c r="R16" s="78"/>
+      <c r="S16" s="79"/>
+      <c r="T16" s="80">
         <f t="shared" ref="T16:T22" si="1">K16*N16*Q16</f>
         <v>0</v>
       </c>
-      <c r="U16" s="106"/>
-      <c r="V16" s="106"/>
-      <c r="W16" s="106"/>
-      <c r="X16" s="106"/>
-      <c r="Y16" s="106"/>
-      <c r="Z16" s="106">
+      <c r="U16" s="80"/>
+      <c r="V16" s="80"/>
+      <c r="W16" s="80"/>
+      <c r="X16" s="80"/>
+      <c r="Y16" s="80"/>
+      <c r="Z16" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="106"/>
-      <c r="AB16" s="106"/>
-      <c r="AC16" s="106"/>
-      <c r="AD16" s="106"/>
-      <c r="AE16" s="98"/>
-      <c r="AF16" s="99"/>
+      <c r="AA16" s="80"/>
+      <c r="AB16" s="80"/>
+      <c r="AC16" s="80"/>
+      <c r="AD16" s="80"/>
+      <c r="AE16" s="81"/>
+      <c r="AF16" s="82"/>
       <c r="AH16" s="19"/>
       <c r="AI16" s="16"/>
       <c r="AJ16" s="15"/>
@@ -2551,46 +2596,46 @@
     </row>
     <row r="17" spans="2:40" s="14" customFormat="1" ht="40.5" customHeight="1">
       <c r="B17" s="13"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="100"/>
-      <c r="E17" s="100"/>
-      <c r="F17" s="100"/>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="101">
+      <c r="C17" s="36"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="74"/>
+      <c r="I17" s="74"/>
+      <c r="J17" s="74"/>
+      <c r="K17" s="84">
         <v>0</v>
       </c>
-      <c r="L17" s="101"/>
-      <c r="M17" s="101"/>
-      <c r="N17" s="102">
+      <c r="L17" s="84"/>
+      <c r="M17" s="84"/>
+      <c r="N17" s="76">
         <v>0</v>
       </c>
-      <c r="O17" s="102"/>
-      <c r="P17" s="102"/>
-      <c r="Q17" s="103"/>
-      <c r="R17" s="104"/>
-      <c r="S17" s="105"/>
-      <c r="T17" s="106">
+      <c r="O17" s="76"/>
+      <c r="P17" s="76"/>
+      <c r="Q17" s="77"/>
+      <c r="R17" s="78"/>
+      <c r="S17" s="79"/>
+      <c r="T17" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U17" s="106"/>
-      <c r="V17" s="106"/>
-      <c r="W17" s="106"/>
-      <c r="X17" s="106"/>
-      <c r="Y17" s="106"/>
-      <c r="Z17" s="106">
+      <c r="U17" s="80"/>
+      <c r="V17" s="80"/>
+      <c r="W17" s="80"/>
+      <c r="X17" s="80"/>
+      <c r="Y17" s="80"/>
+      <c r="Z17" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA17" s="106"/>
-      <c r="AB17" s="106"/>
-      <c r="AC17" s="106"/>
-      <c r="AD17" s="106"/>
-      <c r="AE17" s="98"/>
-      <c r="AF17" s="99"/>
+      <c r="AA17" s="80"/>
+      <c r="AB17" s="80"/>
+      <c r="AC17" s="80"/>
+      <c r="AD17" s="80"/>
+      <c r="AE17" s="81"/>
+      <c r="AF17" s="82"/>
       <c r="AH17" s="19"/>
       <c r="AI17" s="16"/>
       <c r="AJ17" s="15"/>
@@ -2602,45 +2647,45 @@
     <row r="18" spans="2:40" s="14" customFormat="1" ht="40.5" hidden="1" customHeight="1">
       <c r="B18" s="20"/>
       <c r="C18" s="21"/>
-      <c r="D18" s="91" t="s">
+      <c r="D18" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="91"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="91"/>
-      <c r="K18" s="101"/>
-      <c r="L18" s="101"/>
-      <c r="M18" s="101"/>
-      <c r="N18" s="102"/>
-      <c r="O18" s="102"/>
-      <c r="P18" s="102"/>
-      <c r="Q18" s="103">
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
+      <c r="G18" s="88"/>
+      <c r="H18" s="88"/>
+      <c r="I18" s="88"/>
+      <c r="J18" s="88"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="76"/>
+      <c r="O18" s="76"/>
+      <c r="P18" s="76"/>
+      <c r="Q18" s="77">
         <v>1200000</v>
       </c>
-      <c r="R18" s="104"/>
-      <c r="S18" s="105"/>
-      <c r="T18" s="97">
+      <c r="R18" s="78"/>
+      <c r="S18" s="79"/>
+      <c r="T18" s="85">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U18" s="97"/>
-      <c r="V18" s="97"/>
-      <c r="W18" s="97"/>
-      <c r="X18" s="97"/>
-      <c r="Y18" s="97"/>
-      <c r="Z18" s="97">
+      <c r="U18" s="85"/>
+      <c r="V18" s="85"/>
+      <c r="W18" s="85"/>
+      <c r="X18" s="85"/>
+      <c r="Y18" s="85"/>
+      <c r="Z18" s="85">
         <f>T18*10%</f>
         <v>0</v>
       </c>
-      <c r="AA18" s="97"/>
-      <c r="AB18" s="97"/>
-      <c r="AC18" s="97"/>
-      <c r="AD18" s="97"/>
-      <c r="AE18" s="89"/>
-      <c r="AF18" s="90"/>
+      <c r="AA18" s="85"/>
+      <c r="AB18" s="85"/>
+      <c r="AC18" s="85"/>
+      <c r="AD18" s="85"/>
+      <c r="AE18" s="86"/>
+      <c r="AF18" s="87"/>
       <c r="AH18" s="15"/>
       <c r="AI18" s="16"/>
       <c r="AJ18" s="15"/>
@@ -2652,45 +2697,45 @@
     <row r="19" spans="2:40" s="14" customFormat="1" ht="40.5" hidden="1" customHeight="1">
       <c r="B19" s="17"/>
       <c r="C19" s="18"/>
-      <c r="D19" s="100" t="s">
+      <c r="D19" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="100"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="100"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="101"/>
-      <c r="L19" s="101"/>
-      <c r="M19" s="101"/>
-      <c r="N19" s="102"/>
-      <c r="O19" s="102"/>
-      <c r="P19" s="102"/>
-      <c r="Q19" s="103">
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
+      <c r="J19" s="74"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="76"/>
+      <c r="O19" s="76"/>
+      <c r="P19" s="76"/>
+      <c r="Q19" s="77">
         <v>160000</v>
       </c>
-      <c r="R19" s="104"/>
-      <c r="S19" s="105"/>
-      <c r="T19" s="97">
+      <c r="R19" s="78"/>
+      <c r="S19" s="79"/>
+      <c r="T19" s="85">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U19" s="97"/>
-      <c r="V19" s="97"/>
-      <c r="W19" s="97"/>
-      <c r="X19" s="97"/>
-      <c r="Y19" s="97"/>
-      <c r="Z19" s="97">
+      <c r="U19" s="85"/>
+      <c r="V19" s="85"/>
+      <c r="W19" s="85"/>
+      <c r="X19" s="85"/>
+      <c r="Y19" s="85"/>
+      <c r="Z19" s="85">
         <f>T19*10%</f>
         <v>0</v>
       </c>
-      <c r="AA19" s="97"/>
-      <c r="AB19" s="97"/>
-      <c r="AC19" s="97"/>
-      <c r="AD19" s="97"/>
-      <c r="AE19" s="98"/>
-      <c r="AF19" s="99"/>
+      <c r="AA19" s="85"/>
+      <c r="AB19" s="85"/>
+      <c r="AC19" s="85"/>
+      <c r="AD19" s="85"/>
+      <c r="AE19" s="81"/>
+      <c r="AF19" s="82"/>
       <c r="AH19" s="19"/>
       <c r="AI19" s="16"/>
       <c r="AJ19" s="15"/>
@@ -2702,45 +2747,45 @@
     <row r="20" spans="2:40" s="14" customFormat="1" ht="40.5" hidden="1" customHeight="1">
       <c r="B20" s="20"/>
       <c r="C20" s="21"/>
-      <c r="D20" s="91" t="s">
+      <c r="D20" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="91"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="91"/>
-      <c r="K20" s="92"/>
-      <c r="L20" s="92"/>
-      <c r="M20" s="92"/>
-      <c r="N20" s="93"/>
-      <c r="O20" s="93"/>
-      <c r="P20" s="93"/>
-      <c r="Q20" s="94">
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="88"/>
+      <c r="I20" s="88"/>
+      <c r="J20" s="88"/>
+      <c r="K20" s="89"/>
+      <c r="L20" s="89"/>
+      <c r="M20" s="89"/>
+      <c r="N20" s="90"/>
+      <c r="O20" s="90"/>
+      <c r="P20" s="90"/>
+      <c r="Q20" s="91">
         <v>96000</v>
       </c>
-      <c r="R20" s="95"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="97">
+      <c r="R20" s="92"/>
+      <c r="S20" s="93"/>
+      <c r="T20" s="85">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U20" s="97"/>
-      <c r="V20" s="97"/>
-      <c r="W20" s="97"/>
-      <c r="X20" s="97"/>
-      <c r="Y20" s="97"/>
-      <c r="Z20" s="97">
+      <c r="U20" s="85"/>
+      <c r="V20" s="85"/>
+      <c r="W20" s="85"/>
+      <c r="X20" s="85"/>
+      <c r="Y20" s="85"/>
+      <c r="Z20" s="85">
         <f>T20*10%</f>
         <v>0</v>
       </c>
-      <c r="AA20" s="97"/>
-      <c r="AB20" s="97"/>
-      <c r="AC20" s="97"/>
-      <c r="AD20" s="97"/>
-      <c r="AE20" s="89"/>
-      <c r="AF20" s="90"/>
+      <c r="AA20" s="85"/>
+      <c r="AB20" s="85"/>
+      <c r="AC20" s="85"/>
+      <c r="AD20" s="85"/>
+      <c r="AE20" s="86"/>
+      <c r="AF20" s="87"/>
       <c r="AH20" s="15"/>
       <c r="AI20" s="16"/>
       <c r="AJ20" s="15"/>
@@ -2752,45 +2797,45 @@
     <row r="21" spans="2:40" s="14" customFormat="1" ht="40.5" hidden="1" customHeight="1">
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
-      <c r="D21" s="100" t="s">
+      <c r="D21" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="100"/>
-      <c r="F21" s="100"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="100"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="101"/>
-      <c r="L21" s="101"/>
-      <c r="M21" s="101"/>
-      <c r="N21" s="102"/>
-      <c r="O21" s="102"/>
-      <c r="P21" s="102"/>
-      <c r="Q21" s="103">
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="74"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="76"/>
+      <c r="O21" s="76"/>
+      <c r="P21" s="76"/>
+      <c r="Q21" s="77">
         <v>560000</v>
       </c>
-      <c r="R21" s="104"/>
-      <c r="S21" s="105"/>
-      <c r="T21" s="106">
+      <c r="R21" s="78"/>
+      <c r="S21" s="79"/>
+      <c r="T21" s="80">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U21" s="106"/>
-      <c r="V21" s="106"/>
-      <c r="W21" s="106"/>
-      <c r="X21" s="106"/>
-      <c r="Y21" s="106"/>
-      <c r="Z21" s="106">
+      <c r="U21" s="80"/>
+      <c r="V21" s="80"/>
+      <c r="W21" s="80"/>
+      <c r="X21" s="80"/>
+      <c r="Y21" s="80"/>
+      <c r="Z21" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AA21" s="106"/>
-      <c r="AB21" s="106"/>
-      <c r="AC21" s="106"/>
-      <c r="AD21" s="106"/>
-      <c r="AE21" s="98"/>
-      <c r="AF21" s="99"/>
+      <c r="AA21" s="80"/>
+      <c r="AB21" s="80"/>
+      <c r="AC21" s="80"/>
+      <c r="AD21" s="80"/>
+      <c r="AE21" s="81"/>
+      <c r="AF21" s="82"/>
       <c r="AH21" s="19"/>
       <c r="AI21" s="16"/>
       <c r="AJ21" s="15"/>
@@ -2802,45 +2847,45 @@
     <row r="22" spans="2:40" s="14" customFormat="1" ht="40.5" hidden="1" customHeight="1">
       <c r="B22" s="20"/>
       <c r="C22" s="21"/>
-      <c r="D22" s="91" t="s">
+      <c r="D22" s="88" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="91"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="91"/>
-      <c r="H22" s="91"/>
-      <c r="I22" s="91"/>
-      <c r="J22" s="91"/>
-      <c r="K22" s="92"/>
-      <c r="L22" s="92"/>
-      <c r="M22" s="92"/>
-      <c r="N22" s="93"/>
-      <c r="O22" s="93"/>
-      <c r="P22" s="93"/>
-      <c r="Q22" s="94">
+      <c r="E22" s="88"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="88"/>
+      <c r="H22" s="88"/>
+      <c r="I22" s="88"/>
+      <c r="J22" s="88"/>
+      <c r="K22" s="89"/>
+      <c r="L22" s="89"/>
+      <c r="M22" s="89"/>
+      <c r="N22" s="90"/>
+      <c r="O22" s="90"/>
+      <c r="P22" s="90"/>
+      <c r="Q22" s="91">
         <v>250000</v>
       </c>
-      <c r="R22" s="95"/>
-      <c r="S22" s="96"/>
-      <c r="T22" s="97">
+      <c r="R22" s="92"/>
+      <c r="S22" s="93"/>
+      <c r="T22" s="85">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U22" s="97"/>
-      <c r="V22" s="97"/>
-      <c r="W22" s="97"/>
-      <c r="X22" s="97"/>
-      <c r="Y22" s="97"/>
-      <c r="Z22" s="97">
+      <c r="U22" s="85"/>
+      <c r="V22" s="85"/>
+      <c r="W22" s="85"/>
+      <c r="X22" s="85"/>
+      <c r="Y22" s="85"/>
+      <c r="Z22" s="85">
         <f>T22*10%</f>
         <v>0</v>
       </c>
-      <c r="AA22" s="97"/>
-      <c r="AB22" s="97"/>
-      <c r="AC22" s="97"/>
-      <c r="AD22" s="97"/>
-      <c r="AE22" s="89"/>
-      <c r="AF22" s="90"/>
+      <c r="AA22" s="85"/>
+      <c r="AB22" s="85"/>
+      <c r="AC22" s="85"/>
+      <c r="AD22" s="85"/>
+      <c r="AE22" s="86"/>
+      <c r="AF22" s="87"/>
       <c r="AH22" s="15"/>
       <c r="AI22" s="16"/>
       <c r="AJ22" s="15"/>
@@ -2852,35 +2897,35 @@
     <row r="23" spans="2:40" s="14" customFormat="1" ht="40.5" customHeight="1">
       <c r="B23" s="20"/>
       <c r="C23" s="21"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="91"/>
-      <c r="H23" s="91"/>
-      <c r="I23" s="91"/>
-      <c r="J23" s="91"/>
-      <c r="K23" s="92"/>
-      <c r="L23" s="92"/>
-      <c r="M23" s="92"/>
-      <c r="N23" s="93"/>
-      <c r="O23" s="93"/>
-      <c r="P23" s="93"/>
-      <c r="Q23" s="94"/>
-      <c r="R23" s="95"/>
-      <c r="S23" s="96"/>
-      <c r="T23" s="97"/>
-      <c r="U23" s="97"/>
-      <c r="V23" s="97"/>
-      <c r="W23" s="97"/>
-      <c r="X23" s="97"/>
-      <c r="Y23" s="97"/>
-      <c r="Z23" s="97"/>
-      <c r="AA23" s="97"/>
-      <c r="AB23" s="97"/>
-      <c r="AC23" s="97"/>
-      <c r="AD23" s="97"/>
-      <c r="AE23" s="89"/>
-      <c r="AF23" s="90"/>
+      <c r="D23" s="88"/>
+      <c r="E23" s="88"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
+      <c r="I23" s="88"/>
+      <c r="J23" s="88"/>
+      <c r="K23" s="89"/>
+      <c r="L23" s="89"/>
+      <c r="M23" s="89"/>
+      <c r="N23" s="90"/>
+      <c r="O23" s="90"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="91"/>
+      <c r="R23" s="92"/>
+      <c r="S23" s="93"/>
+      <c r="T23" s="85"/>
+      <c r="U23" s="85"/>
+      <c r="V23" s="85"/>
+      <c r="W23" s="85"/>
+      <c r="X23" s="85"/>
+      <c r="Y23" s="85"/>
+      <c r="Z23" s="85"/>
+      <c r="AA23" s="85"/>
+      <c r="AB23" s="85"/>
+      <c r="AC23" s="85"/>
+      <c r="AD23" s="85"/>
+      <c r="AE23" s="86"/>
+      <c r="AF23" s="87"/>
       <c r="AI23" s="19"/>
       <c r="AJ23" s="29"/>
       <c r="AK23" s="15"/>
@@ -2891,35 +2936,35 @@
     <row r="24" spans="2:40" s="14" customFormat="1" ht="40.5" customHeight="1">
       <c r="B24" s="20"/>
       <c r="C24" s="21"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="91"/>
-      <c r="I24" s="91"/>
-      <c r="J24" s="91"/>
-      <c r="K24" s="92"/>
-      <c r="L24" s="92"/>
-      <c r="M24" s="92"/>
-      <c r="N24" s="93"/>
-      <c r="O24" s="93"/>
-      <c r="P24" s="93"/>
-      <c r="Q24" s="94"/>
-      <c r="R24" s="95"/>
-      <c r="S24" s="96"/>
-      <c r="T24" s="97"/>
-      <c r="U24" s="97"/>
-      <c r="V24" s="97"/>
-      <c r="W24" s="97"/>
-      <c r="X24" s="97"/>
-      <c r="Y24" s="97"/>
-      <c r="Z24" s="97"/>
-      <c r="AA24" s="97"/>
-      <c r="AB24" s="97"/>
-      <c r="AC24" s="97"/>
-      <c r="AD24" s="97"/>
-      <c r="AE24" s="89"/>
-      <c r="AF24" s="90"/>
+      <c r="D24" s="88"/>
+      <c r="E24" s="88"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="88"/>
+      <c r="I24" s="88"/>
+      <c r="J24" s="88"/>
+      <c r="K24" s="89"/>
+      <c r="L24" s="89"/>
+      <c r="M24" s="89"/>
+      <c r="N24" s="90"/>
+      <c r="O24" s="90"/>
+      <c r="P24" s="90"/>
+      <c r="Q24" s="91"/>
+      <c r="R24" s="92"/>
+      <c r="S24" s="93"/>
+      <c r="T24" s="85"/>
+      <c r="U24" s="85"/>
+      <c r="V24" s="85"/>
+      <c r="W24" s="85"/>
+      <c r="X24" s="85"/>
+      <c r="Y24" s="85"/>
+      <c r="Z24" s="85"/>
+      <c r="AA24" s="85"/>
+      <c r="AB24" s="85"/>
+      <c r="AC24" s="85"/>
+      <c r="AD24" s="85"/>
+      <c r="AE24" s="86"/>
+      <c r="AF24" s="87"/>
       <c r="AH24" s="15"/>
       <c r="AI24" s="19"/>
       <c r="AJ24" s="15"/>
@@ -2929,214 +2974,214 @@
       <c r="AN24" s="15"/>
     </row>
     <row r="25" spans="2:40" ht="36" customHeight="1">
-      <c r="B25" s="84" t="s">
+      <c r="B25" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="85"/>
-      <c r="D25" s="85"/>
-      <c r="E25" s="85"/>
-      <c r="F25" s="85"/>
-      <c r="G25" s="85"/>
-      <c r="H25" s="85"/>
-      <c r="I25" s="85"/>
-      <c r="J25" s="85"/>
-      <c r="K25" s="85"/>
-      <c r="L25" s="85"/>
-      <c r="M25" s="85"/>
-      <c r="N25" s="85"/>
-      <c r="O25" s="85"/>
-      <c r="P25" s="85"/>
-      <c r="Q25" s="85"/>
-      <c r="R25" s="85"/>
-      <c r="S25" s="86"/>
-      <c r="T25" s="87">
+      <c r="C25" s="95"/>
+      <c r="D25" s="95"/>
+      <c r="E25" s="95"/>
+      <c r="F25" s="95"/>
+      <c r="G25" s="95"/>
+      <c r="H25" s="95"/>
+      <c r="I25" s="95"/>
+      <c r="J25" s="95"/>
+      <c r="K25" s="95"/>
+      <c r="L25" s="95"/>
+      <c r="M25" s="95"/>
+      <c r="N25" s="95"/>
+      <c r="O25" s="95"/>
+      <c r="P25" s="95"/>
+      <c r="Q25" s="95"/>
+      <c r="R25" s="95"/>
+      <c r="S25" s="96"/>
+      <c r="T25" s="97">
         <f>SUM(T10:T24)</f>
         <v>0</v>
       </c>
-      <c r="U25" s="87"/>
-      <c r="V25" s="87"/>
-      <c r="W25" s="87"/>
-      <c r="X25" s="87"/>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87">
+      <c r="U25" s="97"/>
+      <c r="V25" s="97"/>
+      <c r="W25" s="97"/>
+      <c r="X25" s="97"/>
+      <c r="Y25" s="97"/>
+      <c r="Z25" s="97">
         <f>T25*0.1</f>
         <v>0</v>
       </c>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
-      <c r="AE25" s="81"/>
-      <c r="AF25" s="83"/>
-      <c r="AI25" s="34"/>
+      <c r="AA25" s="97"/>
+      <c r="AB25" s="97"/>
+      <c r="AC25" s="97"/>
+      <c r="AD25" s="97"/>
+      <c r="AE25" s="98"/>
+      <c r="AF25" s="99"/>
+      <c r="AI25" s="33"/>
     </row>
     <row r="26" spans="2:40" ht="36" customHeight="1">
-      <c r="B26" s="84" t="s">
+      <c r="B26" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="85"/>
-      <c r="D26" s="85"/>
-      <c r="E26" s="85"/>
-      <c r="F26" s="85"/>
-      <c r="G26" s="85"/>
-      <c r="H26" s="85"/>
-      <c r="I26" s="85"/>
-      <c r="J26" s="85"/>
-      <c r="K26" s="85"/>
-      <c r="L26" s="85"/>
-      <c r="M26" s="85"/>
-      <c r="N26" s="85"/>
-      <c r="O26" s="85"/>
-      <c r="P26" s="85"/>
-      <c r="Q26" s="85"/>
-      <c r="R26" s="85"/>
-      <c r="S26" s="86"/>
-      <c r="T26" s="88">
+      <c r="C26" s="95"/>
+      <c r="D26" s="95"/>
+      <c r="E26" s="95"/>
+      <c r="F26" s="95"/>
+      <c r="G26" s="95"/>
+      <c r="H26" s="95"/>
+      <c r="I26" s="95"/>
+      <c r="J26" s="95"/>
+      <c r="K26" s="95"/>
+      <c r="L26" s="95"/>
+      <c r="M26" s="95"/>
+      <c r="N26" s="95"/>
+      <c r="O26" s="95"/>
+      <c r="P26" s="95"/>
+      <c r="Q26" s="95"/>
+      <c r="R26" s="95"/>
+      <c r="S26" s="96"/>
+      <c r="T26" s="100">
         <f>SUM(T25:AD25)</f>
         <v>0</v>
       </c>
-      <c r="U26" s="69"/>
-      <c r="V26" s="69"/>
-      <c r="W26" s="69"/>
-      <c r="X26" s="69"/>
-      <c r="Y26" s="69"/>
-      <c r="Z26" s="69"/>
-      <c r="AA26" s="69"/>
-      <c r="AB26" s="69"/>
-      <c r="AC26" s="69"/>
-      <c r="AD26" s="70"/>
-      <c r="AE26" s="81"/>
-      <c r="AF26" s="83"/>
+      <c r="U26" s="101"/>
+      <c r="V26" s="101"/>
+      <c r="W26" s="101"/>
+      <c r="X26" s="101"/>
+      <c r="Y26" s="101"/>
+      <c r="Z26" s="101"/>
+      <c r="AA26" s="101"/>
+      <c r="AB26" s="101"/>
+      <c r="AC26" s="101"/>
+      <c r="AD26" s="102"/>
+      <c r="AE26" s="98"/>
+      <c r="AF26" s="99"/>
     </row>
     <row r="27" spans="2:40" ht="40.5" hidden="1" customHeight="1">
-      <c r="B27" s="65" t="s">
+      <c r="B27" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="66"/>
-      <c r="D27" s="66"/>
-      <c r="E27" s="66"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="66"/>
-      <c r="I27" s="66"/>
-      <c r="J27" s="66"/>
-      <c r="K27" s="66"/>
-      <c r="L27" s="66"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="66"/>
-      <c r="P27" s="67"/>
-      <c r="Q27" s="68"/>
-      <c r="R27" s="69"/>
-      <c r="S27" s="70"/>
-      <c r="T27" s="71">
+      <c r="C27" s="104"/>
+      <c r="D27" s="104"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="104"/>
+      <c r="G27" s="104"/>
+      <c r="H27" s="104"/>
+      <c r="I27" s="104"/>
+      <c r="J27" s="104"/>
+      <c r="K27" s="104"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="104"/>
+      <c r="O27" s="104"/>
+      <c r="P27" s="105"/>
+      <c r="Q27" s="106"/>
+      <c r="R27" s="101"/>
+      <c r="S27" s="102"/>
+      <c r="T27" s="107">
         <f>-T26*Q27</f>
         <v>0</v>
       </c>
-      <c r="U27" s="72"/>
-      <c r="V27" s="72"/>
-      <c r="W27" s="72"/>
-      <c r="X27" s="72"/>
-      <c r="Y27" s="72"/>
-      <c r="Z27" s="72"/>
-      <c r="AA27" s="72"/>
-      <c r="AB27" s="72"/>
-      <c r="AC27" s="72"/>
-      <c r="AD27" s="73"/>
-      <c r="AE27" s="74"/>
-      <c r="AF27" s="75"/>
+      <c r="U27" s="108"/>
+      <c r="V27" s="108"/>
+      <c r="W27" s="108"/>
+      <c r="X27" s="108"/>
+      <c r="Y27" s="108"/>
+      <c r="Z27" s="108"/>
+      <c r="AA27" s="108"/>
+      <c r="AB27" s="108"/>
+      <c r="AC27" s="108"/>
+      <c r="AD27" s="109"/>
+      <c r="AE27" s="110"/>
+      <c r="AF27" s="111"/>
       <c r="AI27" s="22"/>
     </row>
     <row r="28" spans="2:40" ht="36" customHeight="1">
-      <c r="B28" s="76" t="s">
+      <c r="B28" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="79"/>
-      <c r="G28" s="79"/>
-      <c r="H28" s="79"/>
-      <c r="I28" s="79"/>
-      <c r="J28" s="79"/>
-      <c r="K28" s="79"/>
-      <c r="L28" s="80"/>
-      <c r="M28" s="81" t="s">
+      <c r="C28" s="66"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="112"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="113"/>
+      <c r="J28" s="113"/>
+      <c r="K28" s="113"/>
+      <c r="L28" s="114"/>
+      <c r="M28" s="98" t="s">
         <v>39</v>
       </c>
-      <c r="N28" s="81"/>
-      <c r="O28" s="81"/>
-      <c r="P28" s="81"/>
-      <c r="Q28" s="82">
+      <c r="N28" s="98"/>
+      <c r="O28" s="98"/>
+      <c r="P28" s="98"/>
+      <c r="Q28" s="115">
         <f>SUM(T26:AD27)</f>
         <v>0</v>
       </c>
-      <c r="R28" s="82"/>
-      <c r="S28" s="82"/>
-      <c r="T28" s="82"/>
-      <c r="U28" s="82"/>
-      <c r="V28" s="82"/>
-      <c r="W28" s="82"/>
-      <c r="X28" s="82"/>
-      <c r="Y28" s="81" t="s">
+      <c r="R28" s="115"/>
+      <c r="S28" s="115"/>
+      <c r="T28" s="115"/>
+      <c r="U28" s="115"/>
+      <c r="V28" s="115"/>
+      <c r="W28" s="115"/>
+      <c r="X28" s="115"/>
+      <c r="Y28" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="Z28" s="81"/>
-      <c r="AA28" s="81"/>
-      <c r="AB28" s="81"/>
-      <c r="AC28" s="81"/>
-      <c r="AD28" s="81"/>
-      <c r="AE28" s="81"/>
-      <c r="AF28" s="83"/>
+      <c r="Z28" s="98"/>
+      <c r="AA28" s="98"/>
+      <c r="AB28" s="98"/>
+      <c r="AC28" s="98"/>
+      <c r="AD28" s="98"/>
+      <c r="AE28" s="98"/>
+      <c r="AF28" s="99"/>
     </row>
     <row r="29" spans="2:40" ht="6" customHeight="1">
       <c r="B29" s="23"/>
-      <c r="C29" s="53"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="53"/>
-      <c r="H29" s="53"/>
-      <c r="I29" s="53"/>
-      <c r="J29" s="53"/>
-      <c r="K29" s="53"/>
-      <c r="L29" s="54"/>
-      <c r="M29" s="54"/>
-      <c r="N29" s="54"/>
-      <c r="O29" s="54"/>
-      <c r="P29" s="54"/>
-      <c r="Q29" s="54"/>
-      <c r="R29" s="54"/>
-      <c r="S29" s="54"/>
-      <c r="T29" s="54"/>
-      <c r="U29" s="54"/>
-      <c r="V29" s="54"/>
-      <c r="W29" s="54"/>
-      <c r="X29" s="54"/>
-      <c r="Y29" s="54"/>
-      <c r="Z29" s="54"/>
-      <c r="AA29" s="54"/>
-      <c r="AB29" s="54"/>
-      <c r="AC29" s="54"/>
-      <c r="AD29" s="54"/>
-      <c r="AE29" s="54"/>
-      <c r="AF29" s="55"/>
+      <c r="C29" s="121"/>
+      <c r="D29" s="121"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="121"/>
+      <c r="H29" s="121"/>
+      <c r="I29" s="121"/>
+      <c r="J29" s="121"/>
+      <c r="K29" s="121"/>
+      <c r="L29" s="122"/>
+      <c r="M29" s="122"/>
+      <c r="N29" s="122"/>
+      <c r="O29" s="122"/>
+      <c r="P29" s="122"/>
+      <c r="Q29" s="122"/>
+      <c r="R29" s="122"/>
+      <c r="S29" s="122"/>
+      <c r="T29" s="122"/>
+      <c r="U29" s="122"/>
+      <c r="V29" s="122"/>
+      <c r="W29" s="122"/>
+      <c r="X29" s="122"/>
+      <c r="Y29" s="122"/>
+      <c r="Z29" s="122"/>
+      <c r="AA29" s="122"/>
+      <c r="AB29" s="122"/>
+      <c r="AC29" s="122"/>
+      <c r="AD29" s="122"/>
+      <c r="AE29" s="122"/>
+      <c r="AF29" s="123"/>
     </row>
     <row r="30" spans="2:40" ht="24" customHeight="1">
-      <c r="B30" s="56" t="s">
+      <c r="B30" s="124" t="s">
         <v>41</v>
       </c>
-      <c r="C30" s="57"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="58" t="s">
+      <c r="C30" s="125"/>
+      <c r="D30" s="125"/>
+      <c r="E30" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="F30" s="57"/>
-      <c r="G30" s="57"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="57"/>
-      <c r="J30" s="57"/>
-      <c r="K30" s="59"/>
+      <c r="F30" s="125"/>
+      <c r="G30" s="125"/>
+      <c r="H30" s="125"/>
+      <c r="I30" s="125"/>
+      <c r="J30" s="125"/>
+      <c r="K30" s="127"/>
       <c r="L30" s="24"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
@@ -3144,61 +3189,61 @@
       <c r="P30" s="25"/>
       <c r="Q30" s="25"/>
       <c r="R30" s="25"/>
-      <c r="S30" s="36"/>
-      <c r="T30" s="36"/>
-      <c r="U30" s="36"/>
-      <c r="V30" s="36"/>
-      <c r="W30" s="36"/>
-      <c r="X30" s="36"/>
-      <c r="Y30" s="36"/>
-      <c r="Z30" s="60"/>
-      <c r="AA30" s="60"/>
-      <c r="AB30" s="60"/>
-      <c r="AC30" s="36"/>
-      <c r="AD30" s="36"/>
-      <c r="AE30" s="36"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="U30" s="34"/>
+      <c r="V30" s="34"/>
+      <c r="W30" s="34"/>
+      <c r="X30" s="34"/>
+      <c r="Y30" s="34"/>
+      <c r="Z30" s="128"/>
+      <c r="AA30" s="128"/>
+      <c r="AB30" s="128"/>
+      <c r="AC30" s="34"/>
+      <c r="AD30" s="34"/>
+      <c r="AE30" s="34"/>
       <c r="AF30" s="26"/>
     </row>
     <row r="31" spans="2:40" s="7" customFormat="1" ht="28.5" hidden="1" customHeight="1">
-      <c r="B31" s="61" t="s">
+      <c r="B31" s="129" t="s">
         <v>42</v>
       </c>
-      <c r="C31" s="60"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="63"/>
-      <c r="F31" s="63"/>
-      <c r="G31" s="63"/>
-      <c r="H31" s="63"/>
-      <c r="I31" s="64" t="s">
+      <c r="C31" s="128"/>
+      <c r="D31" s="130"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="131"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="132" t="s">
         <v>43</v>
       </c>
-      <c r="J31" s="64"/>
-      <c r="K31" s="64"/>
-      <c r="L31" s="63"/>
-      <c r="M31" s="63"/>
-      <c r="N31" s="63"/>
-      <c r="O31" s="63"/>
-      <c r="P31" s="63"/>
-      <c r="Q31" s="63"/>
-      <c r="R31" s="37" t="s">
+      <c r="J31" s="132"/>
+      <c r="K31" s="132"/>
+      <c r="L31" s="131"/>
+      <c r="M31" s="131"/>
+      <c r="N31" s="131"/>
+      <c r="O31" s="131"/>
+      <c r="P31" s="131"/>
+      <c r="Q31" s="131"/>
+      <c r="R31" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="S31" s="63"/>
-      <c r="T31" s="63"/>
-      <c r="U31" s="63"/>
-      <c r="V31" s="63"/>
-      <c r="W31" s="63"/>
-      <c r="X31" s="64" t="s">
+      <c r="S31" s="131"/>
+      <c r="T31" s="131"/>
+      <c r="U31" s="131"/>
+      <c r="V31" s="131"/>
+      <c r="W31" s="131"/>
+      <c r="X31" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="Y31" s="64"/>
-      <c r="Z31" s="48"/>
-      <c r="AA31" s="49"/>
-      <c r="AB31" s="49"/>
-      <c r="AC31" s="49"/>
-      <c r="AD31" s="49"/>
-      <c r="AE31" s="49"/>
-      <c r="AF31" s="50"/>
+      <c r="Y31" s="132"/>
+      <c r="Z31" s="116"/>
+      <c r="AA31" s="117"/>
+      <c r="AB31" s="117"/>
+      <c r="AC31" s="117"/>
+      <c r="AD31" s="117"/>
+      <c r="AE31" s="117"/>
+      <c r="AF31" s="118"/>
       <c r="AH31" s="4"/>
       <c r="AI31" s="4"/>
       <c r="AJ31" s="4"/>
@@ -3227,18 +3272,18 @@
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
       <c r="T32" s="28"/>
-      <c r="U32" s="51"/>
-      <c r="V32" s="51"/>
-      <c r="W32" s="51"/>
-      <c r="X32" s="51"/>
-      <c r="Y32" s="51"/>
-      <c r="Z32" s="51"/>
-      <c r="AA32" s="51"/>
-      <c r="AB32" s="51"/>
-      <c r="AC32" s="51"/>
-      <c r="AD32" s="51"/>
-      <c r="AE32" s="52"/>
-      <c r="AF32" s="52"/>
+      <c r="U32" s="119"/>
+      <c r="V32" s="119"/>
+      <c r="W32" s="119"/>
+      <c r="X32" s="119"/>
+      <c r="Y32" s="119"/>
+      <c r="Z32" s="119"/>
+      <c r="AA32" s="119"/>
+      <c r="AB32" s="119"/>
+      <c r="AC32" s="119"/>
+      <c r="AD32" s="119"/>
+      <c r="AE32" s="120"/>
+      <c r="AF32" s="120"/>
       <c r="AH32" s="4"/>
       <c r="AI32" s="4"/>
       <c r="AJ32" s="4"/>
@@ -3248,37 +3293,37 @@
       <c r="AN32" s="4"/>
     </row>
     <row r="33" spans="2:40" s="7" customFormat="1" ht="24.95" customHeight="1">
-      <c r="B33" s="46"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="42"/>
-      <c r="L33" s="42"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
-      <c r="P33" s="42"/>
-      <c r="Q33" s="42"/>
-      <c r="R33" s="42"/>
-      <c r="S33" s="42"/>
-      <c r="T33" s="42"/>
-      <c r="U33" s="42"/>
-      <c r="V33" s="42"/>
-      <c r="W33" s="42"/>
-      <c r="X33" s="42"/>
-      <c r="Y33" s="42"/>
-      <c r="Z33" s="42"/>
-      <c r="AA33" s="42"/>
-      <c r="AB33" s="42"/>
-      <c r="AC33" s="42"/>
-      <c r="AD33" s="42"/>
-      <c r="AE33" s="42"/>
-      <c r="AF33" s="42"/>
+      <c r="B33" s="138"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="138"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="139"/>
+      <c r="G33" s="134"/>
+      <c r="H33" s="134"/>
+      <c r="I33" s="134"/>
+      <c r="J33" s="134"/>
+      <c r="K33" s="134"/>
+      <c r="L33" s="134"/>
+      <c r="M33" s="134"/>
+      <c r="N33" s="134"/>
+      <c r="O33" s="134"/>
+      <c r="P33" s="134"/>
+      <c r="Q33" s="134"/>
+      <c r="R33" s="134"/>
+      <c r="S33" s="134"/>
+      <c r="T33" s="134"/>
+      <c r="U33" s="134"/>
+      <c r="V33" s="134"/>
+      <c r="W33" s="134"/>
+      <c r="X33" s="134"/>
+      <c r="Y33" s="134"/>
+      <c r="Z33" s="134"/>
+      <c r="AA33" s="134"/>
+      <c r="AB33" s="134"/>
+      <c r="AC33" s="134"/>
+      <c r="AD33" s="134"/>
+      <c r="AE33" s="134"/>
+      <c r="AF33" s="134"/>
       <c r="AH33" s="4"/>
       <c r="AI33" s="4"/>
       <c r="AJ33" s="4"/>
@@ -3288,37 +3333,37 @@
       <c r="AN33" s="4"/>
     </row>
     <row r="34" spans="2:40" s="7" customFormat="1" ht="24.95" customHeight="1">
-      <c r="B34" s="43"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="43"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="43"/>
-      <c r="N34" s="43"/>
-      <c r="O34" s="43"/>
-      <c r="P34" s="43"/>
-      <c r="Q34" s="43"/>
-      <c r="R34" s="43"/>
-      <c r="S34" s="43"/>
-      <c r="T34" s="43"/>
-      <c r="U34" s="43"/>
-      <c r="V34" s="43"/>
-      <c r="W34" s="43"/>
-      <c r="X34" s="43"/>
-      <c r="Y34" s="43"/>
-      <c r="Z34" s="43"/>
-      <c r="AA34" s="43"/>
-      <c r="AB34" s="43"/>
-      <c r="AC34" s="43"/>
-      <c r="AD34" s="43"/>
-      <c r="AE34" s="43"/>
-      <c r="AF34" s="43"/>
+      <c r="B34" s="135"/>
+      <c r="C34" s="135"/>
+      <c r="D34" s="135"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="135"/>
+      <c r="I34" s="135"/>
+      <c r="J34" s="135"/>
+      <c r="K34" s="135"/>
+      <c r="L34" s="135"/>
+      <c r="M34" s="135"/>
+      <c r="N34" s="135"/>
+      <c r="O34" s="135"/>
+      <c r="P34" s="135"/>
+      <c r="Q34" s="135"/>
+      <c r="R34" s="135"/>
+      <c r="S34" s="135"/>
+      <c r="T34" s="135"/>
+      <c r="U34" s="135"/>
+      <c r="V34" s="135"/>
+      <c r="W34" s="135"/>
+      <c r="X34" s="135"/>
+      <c r="Y34" s="135"/>
+      <c r="Z34" s="135"/>
+      <c r="AA34" s="135"/>
+      <c r="AB34" s="135"/>
+      <c r="AC34" s="135"/>
+      <c r="AD34" s="135"/>
+      <c r="AE34" s="135"/>
+      <c r="AF34" s="135"/>
       <c r="AH34" s="4"/>
       <c r="AI34" s="4"/>
       <c r="AJ34" s="4"/>
@@ -3328,37 +3373,37 @@
       <c r="AN34" s="4"/>
     </row>
     <row r="35" spans="2:40" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="B35" s="43"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="43"/>
-      <c r="Q35" s="43"/>
-      <c r="R35" s="43"/>
-      <c r="S35" s="43"/>
-      <c r="T35" s="43"/>
-      <c r="U35" s="43"/>
-      <c r="V35" s="43"/>
-      <c r="W35" s="43"/>
-      <c r="X35" s="43"/>
-      <c r="Y35" s="43"/>
-      <c r="Z35" s="43"/>
-      <c r="AA35" s="43"/>
-      <c r="AB35" s="43"/>
-      <c r="AC35" s="43"/>
-      <c r="AD35" s="43"/>
-      <c r="AE35" s="43"/>
-      <c r="AF35" s="43"/>
+      <c r="B35" s="135"/>
+      <c r="C35" s="135"/>
+      <c r="D35" s="135"/>
+      <c r="E35" s="135"/>
+      <c r="F35" s="135"/>
+      <c r="G35" s="135"/>
+      <c r="H35" s="135"/>
+      <c r="I35" s="135"/>
+      <c r="J35" s="135"/>
+      <c r="K35" s="135"/>
+      <c r="L35" s="135"/>
+      <c r="M35" s="135"/>
+      <c r="N35" s="135"/>
+      <c r="O35" s="135"/>
+      <c r="P35" s="135"/>
+      <c r="Q35" s="135"/>
+      <c r="R35" s="135"/>
+      <c r="S35" s="135"/>
+      <c r="T35" s="135"/>
+      <c r="U35" s="135"/>
+      <c r="V35" s="135"/>
+      <c r="W35" s="135"/>
+      <c r="X35" s="135"/>
+      <c r="Y35" s="135"/>
+      <c r="Z35" s="135"/>
+      <c r="AA35" s="135"/>
+      <c r="AB35" s="135"/>
+      <c r="AC35" s="135"/>
+      <c r="AD35" s="135"/>
+      <c r="AE35" s="135"/>
+      <c r="AF35" s="135"/>
       <c r="AH35" s="4"/>
       <c r="AI35" s="4"/>
       <c r="AJ35" s="4"/>
@@ -3368,37 +3413,37 @@
       <c r="AN35" s="4"/>
     </row>
     <row r="36" spans="2:40" s="7" customFormat="1" ht="15" customHeight="1">
-      <c r="B36" s="43"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="43"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="43"/>
-      <c r="R36" s="43"/>
-      <c r="S36" s="43"/>
-      <c r="T36" s="43"/>
-      <c r="U36" s="43"/>
-      <c r="V36" s="43"/>
-      <c r="W36" s="43"/>
-      <c r="X36" s="43"/>
-      <c r="Y36" s="43"/>
-      <c r="Z36" s="43"/>
-      <c r="AA36" s="43"/>
-      <c r="AB36" s="43"/>
-      <c r="AC36" s="43"/>
-      <c r="AD36" s="43"/>
-      <c r="AE36" s="43"/>
-      <c r="AF36" s="43"/>
+      <c r="B36" s="135"/>
+      <c r="C36" s="135"/>
+      <c r="D36" s="135"/>
+      <c r="E36" s="135"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="135"/>
+      <c r="I36" s="135"/>
+      <c r="J36" s="135"/>
+      <c r="K36" s="135"/>
+      <c r="L36" s="135"/>
+      <c r="M36" s="135"/>
+      <c r="N36" s="135"/>
+      <c r="O36" s="135"/>
+      <c r="P36" s="135"/>
+      <c r="Q36" s="135"/>
+      <c r="R36" s="135"/>
+      <c r="S36" s="135"/>
+      <c r="T36" s="135"/>
+      <c r="U36" s="135"/>
+      <c r="V36" s="135"/>
+      <c r="W36" s="135"/>
+      <c r="X36" s="135"/>
+      <c r="Y36" s="135"/>
+      <c r="Z36" s="135"/>
+      <c r="AA36" s="135"/>
+      <c r="AB36" s="135"/>
+      <c r="AC36" s="135"/>
+      <c r="AD36" s="135"/>
+      <c r="AE36" s="135"/>
+      <c r="AF36" s="135"/>
       <c r="AH36" s="4"/>
       <c r="AI36" s="4"/>
       <c r="AJ36" s="4"/>
@@ -3408,37 +3453,37 @@
       <c r="AN36" s="4"/>
     </row>
     <row r="37" spans="2:40" s="7" customFormat="1" ht="15" customHeight="1">
-      <c r="B37" s="43"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="43"/>
-      <c r="L37" s="43"/>
-      <c r="M37" s="43"/>
-      <c r="N37" s="43"/>
-      <c r="O37" s="43"/>
-      <c r="P37" s="43"/>
-      <c r="Q37" s="43"/>
-      <c r="R37" s="43"/>
-      <c r="S37" s="43"/>
-      <c r="T37" s="43"/>
-      <c r="U37" s="43"/>
-      <c r="V37" s="43"/>
-      <c r="W37" s="43"/>
-      <c r="X37" s="43"/>
-      <c r="Y37" s="43"/>
-      <c r="Z37" s="43"/>
-      <c r="AA37" s="43"/>
-      <c r="AB37" s="43"/>
-      <c r="AC37" s="43"/>
-      <c r="AD37" s="43"/>
-      <c r="AE37" s="43"/>
-      <c r="AF37" s="43"/>
+      <c r="B37" s="135"/>
+      <c r="C37" s="135"/>
+      <c r="D37" s="135"/>
+      <c r="E37" s="135"/>
+      <c r="F37" s="135"/>
+      <c r="G37" s="135"/>
+      <c r="H37" s="135"/>
+      <c r="I37" s="135"/>
+      <c r="J37" s="135"/>
+      <c r="K37" s="135"/>
+      <c r="L37" s="135"/>
+      <c r="M37" s="135"/>
+      <c r="N37" s="135"/>
+      <c r="O37" s="135"/>
+      <c r="P37" s="135"/>
+      <c r="Q37" s="135"/>
+      <c r="R37" s="135"/>
+      <c r="S37" s="135"/>
+      <c r="T37" s="135"/>
+      <c r="U37" s="135"/>
+      <c r="V37" s="135"/>
+      <c r="W37" s="135"/>
+      <c r="X37" s="135"/>
+      <c r="Y37" s="135"/>
+      <c r="Z37" s="135"/>
+      <c r="AA37" s="135"/>
+      <c r="AB37" s="135"/>
+      <c r="AC37" s="135"/>
+      <c r="AD37" s="135"/>
+      <c r="AE37" s="135"/>
+      <c r="AF37" s="135"/>
       <c r="AH37" s="4"/>
       <c r="AI37" s="4"/>
       <c r="AJ37" s="4"/>
@@ -3448,37 +3493,37 @@
       <c r="AN37" s="4"/>
     </row>
     <row r="38" spans="2:40" s="7" customFormat="1" ht="15" customHeight="1">
-      <c r="B38" s="43"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="43"/>
-      <c r="J38" s="43"/>
-      <c r="K38" s="43"/>
-      <c r="L38" s="43"/>
-      <c r="M38" s="43"/>
-      <c r="N38" s="43"/>
-      <c r="O38" s="43"/>
-      <c r="P38" s="43"/>
-      <c r="Q38" s="43"/>
-      <c r="R38" s="43"/>
-      <c r="S38" s="43"/>
-      <c r="T38" s="43"/>
-      <c r="U38" s="43"/>
-      <c r="V38" s="43"/>
-      <c r="W38" s="43"/>
-      <c r="X38" s="43"/>
-      <c r="Y38" s="43"/>
-      <c r="Z38" s="43"/>
-      <c r="AA38" s="43"/>
-      <c r="AB38" s="43"/>
-      <c r="AC38" s="43"/>
-      <c r="AD38" s="43"/>
-      <c r="AE38" s="43"/>
-      <c r="AF38" s="43"/>
+      <c r="B38" s="135"/>
+      <c r="C38" s="135"/>
+      <c r="D38" s="135"/>
+      <c r="E38" s="135"/>
+      <c r="F38" s="135"/>
+      <c r="G38" s="135"/>
+      <c r="H38" s="135"/>
+      <c r="I38" s="135"/>
+      <c r="J38" s="135"/>
+      <c r="K38" s="135"/>
+      <c r="L38" s="135"/>
+      <c r="M38" s="135"/>
+      <c r="N38" s="135"/>
+      <c r="O38" s="135"/>
+      <c r="P38" s="135"/>
+      <c r="Q38" s="135"/>
+      <c r="R38" s="135"/>
+      <c r="S38" s="135"/>
+      <c r="T38" s="135"/>
+      <c r="U38" s="135"/>
+      <c r="V38" s="135"/>
+      <c r="W38" s="135"/>
+      <c r="X38" s="135"/>
+      <c r="Y38" s="135"/>
+      <c r="Z38" s="135"/>
+      <c r="AA38" s="135"/>
+      <c r="AB38" s="135"/>
+      <c r="AC38" s="135"/>
+      <c r="AD38" s="135"/>
+      <c r="AE38" s="135"/>
+      <c r="AF38" s="135"/>
       <c r="AH38" s="4"/>
       <c r="AI38" s="4"/>
       <c r="AJ38" s="4"/>
@@ -3488,37 +3533,37 @@
       <c r="AN38" s="4"/>
     </row>
     <row r="39" spans="2:40" s="7" customFormat="1" ht="15" customHeight="1">
-      <c r="B39" s="43"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="43"/>
-      <c r="K39" s="43"/>
-      <c r="L39" s="43"/>
-      <c r="M39" s="43"/>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="43"/>
-      <c r="T39" s="43"/>
-      <c r="U39" s="43"/>
-      <c r="V39" s="43"/>
-      <c r="W39" s="43"/>
-      <c r="X39" s="43"/>
-      <c r="Y39" s="43"/>
-      <c r="Z39" s="43"/>
-      <c r="AA39" s="43"/>
-      <c r="AB39" s="43"/>
-      <c r="AC39" s="43"/>
-      <c r="AD39" s="43"/>
-      <c r="AE39" s="43"/>
-      <c r="AF39" s="43"/>
+      <c r="B39" s="135"/>
+      <c r="C39" s="135"/>
+      <c r="D39" s="135"/>
+      <c r="E39" s="135"/>
+      <c r="F39" s="135"/>
+      <c r="G39" s="135"/>
+      <c r="H39" s="135"/>
+      <c r="I39" s="135"/>
+      <c r="J39" s="135"/>
+      <c r="K39" s="135"/>
+      <c r="L39" s="135"/>
+      <c r="M39" s="135"/>
+      <c r="N39" s="135"/>
+      <c r="O39" s="135"/>
+      <c r="P39" s="135"/>
+      <c r="Q39" s="135"/>
+      <c r="R39" s="135"/>
+      <c r="S39" s="135"/>
+      <c r="T39" s="135"/>
+      <c r="U39" s="135"/>
+      <c r="V39" s="135"/>
+      <c r="W39" s="135"/>
+      <c r="X39" s="135"/>
+      <c r="Y39" s="135"/>
+      <c r="Z39" s="135"/>
+      <c r="AA39" s="135"/>
+      <c r="AB39" s="135"/>
+      <c r="AC39" s="135"/>
+      <c r="AD39" s="135"/>
+      <c r="AE39" s="135"/>
+      <c r="AF39" s="135"/>
       <c r="AH39" s="4"/>
       <c r="AI39" s="4"/>
       <c r="AJ39" s="4"/>
@@ -3528,37 +3573,37 @@
       <c r="AN39" s="4"/>
     </row>
     <row r="40" spans="2:40" s="7" customFormat="1" ht="15" customHeight="1">
-      <c r="B40" s="43"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43"/>
-      <c r="J40" s="43"/>
-      <c r="K40" s="43"/>
-      <c r="L40" s="43"/>
-      <c r="M40" s="43"/>
-      <c r="N40" s="43"/>
-      <c r="O40" s="43"/>
-      <c r="P40" s="43"/>
-      <c r="Q40" s="43"/>
-      <c r="R40" s="43"/>
-      <c r="S40" s="43"/>
-      <c r="T40" s="43"/>
-      <c r="U40" s="43"/>
-      <c r="V40" s="43"/>
-      <c r="W40" s="43"/>
-      <c r="X40" s="43"/>
-      <c r="Y40" s="43"/>
-      <c r="Z40" s="43"/>
-      <c r="AA40" s="43"/>
-      <c r="AB40" s="43"/>
-      <c r="AC40" s="43"/>
-      <c r="AD40" s="43"/>
-      <c r="AE40" s="43"/>
-      <c r="AF40" s="43"/>
+      <c r="B40" s="135"/>
+      <c r="C40" s="135"/>
+      <c r="D40" s="135"/>
+      <c r="E40" s="135"/>
+      <c r="F40" s="135"/>
+      <c r="G40" s="135"/>
+      <c r="H40" s="135"/>
+      <c r="I40" s="135"/>
+      <c r="J40" s="135"/>
+      <c r="K40" s="135"/>
+      <c r="L40" s="135"/>
+      <c r="M40" s="135"/>
+      <c r="N40" s="135"/>
+      <c r="O40" s="135"/>
+      <c r="P40" s="135"/>
+      <c r="Q40" s="135"/>
+      <c r="R40" s="135"/>
+      <c r="S40" s="135"/>
+      <c r="T40" s="135"/>
+      <c r="U40" s="135"/>
+      <c r="V40" s="135"/>
+      <c r="W40" s="135"/>
+      <c r="X40" s="135"/>
+      <c r="Y40" s="135"/>
+      <c r="Z40" s="135"/>
+      <c r="AA40" s="135"/>
+      <c r="AB40" s="135"/>
+      <c r="AC40" s="135"/>
+      <c r="AD40" s="135"/>
+      <c r="AE40" s="135"/>
+      <c r="AF40" s="135"/>
       <c r="AH40" s="4"/>
       <c r="AI40" s="4"/>
       <c r="AJ40" s="4"/>
@@ -3568,271 +3613,296 @@
       <c r="AN40" s="4"/>
     </row>
     <row r="41" spans="2:40" ht="24.75" customHeight="1">
-      <c r="B41" s="43"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
-      <c r="L41" s="43"/>
-      <c r="M41" s="43"/>
-      <c r="N41" s="43"/>
-      <c r="O41" s="43"/>
-      <c r="P41" s="43"/>
-      <c r="Q41" s="43"/>
-      <c r="R41" s="43"/>
-      <c r="S41" s="43"/>
-      <c r="T41" s="43"/>
-      <c r="U41" s="43"/>
-      <c r="V41" s="43"/>
-      <c r="W41" s="43"/>
-      <c r="X41" s="43"/>
-      <c r="Y41" s="43"/>
-      <c r="Z41" s="43"/>
-      <c r="AA41" s="43"/>
-      <c r="AB41" s="43"/>
-      <c r="AC41" s="43"/>
-      <c r="AD41" s="43"/>
-      <c r="AE41" s="43"/>
-      <c r="AF41" s="43"/>
+      <c r="B41" s="135"/>
+      <c r="C41" s="135"/>
+      <c r="D41" s="135"/>
+      <c r="E41" s="135"/>
+      <c r="F41" s="135"/>
+      <c r="G41" s="135"/>
+      <c r="H41" s="135"/>
+      <c r="I41" s="135"/>
+      <c r="J41" s="135"/>
+      <c r="K41" s="135"/>
+      <c r="L41" s="135"/>
+      <c r="M41" s="135"/>
+      <c r="N41" s="135"/>
+      <c r="O41" s="135"/>
+      <c r="P41" s="135"/>
+      <c r="Q41" s="135"/>
+      <c r="R41" s="135"/>
+      <c r="S41" s="135"/>
+      <c r="T41" s="135"/>
+      <c r="U41" s="135"/>
+      <c r="V41" s="135"/>
+      <c r="W41" s="135"/>
+      <c r="X41" s="135"/>
+      <c r="Y41" s="135"/>
+      <c r="Z41" s="135"/>
+      <c r="AA41" s="135"/>
+      <c r="AB41" s="135"/>
+      <c r="AC41" s="135"/>
+      <c r="AD41" s="135"/>
+      <c r="AE41" s="135"/>
+      <c r="AF41" s="135"/>
     </row>
     <row r="42" spans="2:40" ht="24.95" customHeight="1">
-      <c r="B42" s="43"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
-      <c r="L42" s="43"/>
-      <c r="M42" s="43"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="43"/>
-      <c r="S42" s="43"/>
-      <c r="T42" s="43"/>
-      <c r="U42" s="43"/>
-      <c r="V42" s="43"/>
-      <c r="W42" s="43"/>
-      <c r="X42" s="43"/>
-      <c r="Y42" s="43"/>
-      <c r="Z42" s="43"/>
-      <c r="AA42" s="43"/>
-      <c r="AB42" s="43"/>
-      <c r="AC42" s="43"/>
-      <c r="AD42" s="43"/>
-      <c r="AE42" s="43"/>
-      <c r="AF42" s="43"/>
+      <c r="B42" s="135"/>
+      <c r="C42" s="135"/>
+      <c r="D42" s="135"/>
+      <c r="E42" s="135"/>
+      <c r="F42" s="135"/>
+      <c r="G42" s="135"/>
+      <c r="H42" s="135"/>
+      <c r="I42" s="135"/>
+      <c r="J42" s="135"/>
+      <c r="K42" s="135"/>
+      <c r="L42" s="135"/>
+      <c r="M42" s="135"/>
+      <c r="N42" s="135"/>
+      <c r="O42" s="135"/>
+      <c r="P42" s="135"/>
+      <c r="Q42" s="135"/>
+      <c r="R42" s="135"/>
+      <c r="S42" s="135"/>
+      <c r="T42" s="135"/>
+      <c r="U42" s="135"/>
+      <c r="V42" s="135"/>
+      <c r="W42" s="135"/>
+      <c r="X42" s="135"/>
+      <c r="Y42" s="135"/>
+      <c r="Z42" s="135"/>
+      <c r="AA42" s="135"/>
+      <c r="AB42" s="135"/>
+      <c r="AC42" s="135"/>
+      <c r="AD42" s="135"/>
+      <c r="AE42" s="135"/>
+      <c r="AF42" s="135"/>
     </row>
     <row r="43" spans="2:40" ht="24.95" customHeight="1">
-      <c r="B43" s="35"/>
-      <c r="C43" s="35"/>
-      <c r="D43" s="35"/>
-      <c r="E43" s="35"/>
-      <c r="F43" s="35"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="35"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="35"/>
-      <c r="L43" s="35"/>
-      <c r="M43" s="35"/>
-      <c r="N43" s="35"/>
-      <c r="O43" s="35"/>
-      <c r="P43" s="35"/>
-      <c r="Q43" s="35"/>
-      <c r="R43" s="35"/>
-      <c r="S43" s="35"/>
-      <c r="T43" s="35"/>
-      <c r="U43" s="35"/>
-      <c r="V43" s="35"/>
-      <c r="W43" s="35"/>
-      <c r="X43" s="35"/>
-      <c r="Y43" s="44"/>
-      <c r="Z43" s="44"/>
-      <c r="AA43" s="44"/>
-      <c r="AB43" s="44"/>
-      <c r="AC43" s="44"/>
-      <c r="AD43" s="44"/>
-      <c r="AE43" s="44"/>
-      <c r="AF43" s="35"/>
+      <c r="Y43" s="136"/>
+      <c r="Z43" s="136"/>
+      <c r="AA43" s="136"/>
+      <c r="AB43" s="136"/>
+      <c r="AC43" s="136"/>
+      <c r="AD43" s="136"/>
+      <c r="AE43" s="136"/>
     </row>
     <row r="44" spans="2:40" ht="24.95" customHeight="1">
-      <c r="B44" s="35"/>
-      <c r="C44" s="35"/>
-      <c r="D44" s="35"/>
-      <c r="E44" s="35"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="35"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="35"/>
-      <c r="J44" s="35"/>
-      <c r="K44" s="35"/>
-      <c r="L44" s="35"/>
-      <c r="M44" s="35"/>
-      <c r="N44" s="35"/>
-      <c r="O44" s="35"/>
-      <c r="P44" s="35"/>
-      <c r="Q44" s="35"/>
-      <c r="R44" s="35"/>
-      <c r="S44" s="35"/>
-      <c r="T44" s="35"/>
-      <c r="U44" s="35"/>
-      <c r="V44" s="35"/>
-      <c r="W44" s="35"/>
-      <c r="X44" s="35"/>
-      <c r="Y44" s="45"/>
-      <c r="Z44" s="46"/>
-      <c r="AA44" s="46"/>
-      <c r="AB44" s="46"/>
-      <c r="AC44" s="46"/>
-      <c r="AD44" s="46"/>
-      <c r="AE44" s="46"/>
-      <c r="AF44" s="35"/>
-    </row>
-    <row r="45" spans="2:40" ht="24.95" customHeight="1">
-      <c r="B45" s="35"/>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="35"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="35"/>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="35"/>
-      <c r="L45" s="35"/>
-      <c r="M45" s="35"/>
-      <c r="N45" s="35"/>
-      <c r="O45" s="35"/>
-      <c r="P45" s="35"/>
-      <c r="Q45" s="35"/>
-      <c r="R45" s="35"/>
-      <c r="S45" s="35"/>
-      <c r="T45" s="35"/>
-      <c r="U45" s="35"/>
-      <c r="V45" s="35"/>
-      <c r="W45" s="35"/>
-      <c r="X45" s="35"/>
-      <c r="Y45" s="35"/>
-      <c r="Z45" s="35"/>
-      <c r="AA45" s="35"/>
-      <c r="AB45" s="35"/>
-      <c r="AC45" s="35"/>
-      <c r="AD45" s="35"/>
-      <c r="AE45" s="35"/>
-      <c r="AF45" s="35"/>
+      <c r="Y44" s="137"/>
+      <c r="Z44" s="138"/>
+      <c r="AA44" s="138"/>
+      <c r="AB44" s="138"/>
+      <c r="AC44" s="138"/>
+      <c r="AD44" s="138"/>
+      <c r="AE44" s="138"/>
     </row>
     <row r="46" spans="2:40" ht="24.95" customHeight="1">
-      <c r="B46" s="41" t="s">
+      <c r="B46" s="133" t="s">
         <v>6</v>
       </c>
-      <c r="C46" s="41"/>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="41"/>
-      <c r="M46" s="41"/>
-      <c r="N46" s="41"/>
-      <c r="O46" s="41"/>
-      <c r="P46" s="41"/>
-      <c r="Q46" s="41"/>
-      <c r="R46" s="41"/>
-      <c r="S46" s="41"/>
-      <c r="T46" s="41"/>
-      <c r="U46" s="41"/>
-      <c r="V46" s="41"/>
-      <c r="W46" s="41"/>
-      <c r="X46" s="41"/>
-      <c r="Y46" s="41"/>
-      <c r="Z46" s="41"/>
-      <c r="AA46" s="41"/>
-      <c r="AB46" s="41"/>
-      <c r="AC46" s="41"/>
-      <c r="AD46" s="41"/>
-      <c r="AE46" s="41"/>
-      <c r="AF46" s="41"/>
+      <c r="C46" s="133"/>
+      <c r="D46" s="133"/>
+      <c r="E46" s="133"/>
+      <c r="F46" s="133"/>
+      <c r="G46" s="133"/>
+      <c r="H46" s="133"/>
+      <c r="I46" s="133"/>
+      <c r="J46" s="133"/>
+      <c r="K46" s="133"/>
+      <c r="L46" s="133"/>
+      <c r="M46" s="133"/>
+      <c r="N46" s="133"/>
+      <c r="O46" s="133"/>
+      <c r="P46" s="133"/>
+      <c r="Q46" s="133"/>
+      <c r="R46" s="133"/>
+      <c r="S46" s="133"/>
+      <c r="T46" s="133"/>
+      <c r="U46" s="133"/>
+      <c r="V46" s="133"/>
+      <c r="W46" s="133"/>
+      <c r="X46" s="133"/>
+      <c r="Y46" s="133"/>
+      <c r="Z46" s="133"/>
+      <c r="AA46" s="133"/>
+      <c r="AB46" s="133"/>
+      <c r="AC46" s="133"/>
+      <c r="AD46" s="133"/>
+      <c r="AE46" s="133"/>
+      <c r="AF46" s="133"/>
     </row>
     <row r="47" spans="2:40" ht="24.95" customHeight="1">
-      <c r="B47" s="41"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="41"/>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="41"/>
-      <c r="M47" s="41"/>
-      <c r="N47" s="41"/>
-      <c r="O47" s="41"/>
-      <c r="P47" s="41"/>
-      <c r="Q47" s="41"/>
-      <c r="R47" s="41"/>
-      <c r="S47" s="41"/>
-      <c r="T47" s="41"/>
-      <c r="U47" s="41"/>
-      <c r="V47" s="41"/>
-      <c r="W47" s="41"/>
-      <c r="X47" s="41"/>
-      <c r="Y47" s="41"/>
-      <c r="Z47" s="41"/>
-      <c r="AA47" s="41"/>
-      <c r="AB47" s="41"/>
-      <c r="AC47" s="41"/>
-      <c r="AD47" s="41"/>
-      <c r="AE47" s="41"/>
-      <c r="AF47" s="41"/>
+      <c r="B47" s="133"/>
+      <c r="C47" s="133"/>
+      <c r="D47" s="133"/>
+      <c r="E47" s="133"/>
+      <c r="F47" s="133"/>
+      <c r="G47" s="133"/>
+      <c r="H47" s="133"/>
+      <c r="I47" s="133"/>
+      <c r="J47" s="133"/>
+      <c r="K47" s="133"/>
+      <c r="L47" s="133"/>
+      <c r="M47" s="133"/>
+      <c r="N47" s="133"/>
+      <c r="O47" s="133"/>
+      <c r="P47" s="133"/>
+      <c r="Q47" s="133"/>
+      <c r="R47" s="133"/>
+      <c r="S47" s="133"/>
+      <c r="T47" s="133"/>
+      <c r="U47" s="133"/>
+      <c r="V47" s="133"/>
+      <c r="W47" s="133"/>
+      <c r="X47" s="133"/>
+      <c r="Y47" s="133"/>
+      <c r="Z47" s="133"/>
+      <c r="AA47" s="133"/>
+      <c r="AB47" s="133"/>
+      <c r="AC47" s="133"/>
+      <c r="AD47" s="133"/>
+      <c r="AE47" s="133"/>
+      <c r="AF47" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="189">
-    <mergeCell ref="B2:AF2"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="K3:K6"/>
-    <mergeCell ref="L3:O3"/>
-    <mergeCell ref="P3:AF3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="P4:W4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AF4"/>
-    <mergeCell ref="B5:J5"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="P5:AF5"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="X6:AF6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="G7:AD7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="G8:P8"/>
-    <mergeCell ref="T8:AE8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="T9:Y9"/>
-    <mergeCell ref="Z9:AD9"/>
-    <mergeCell ref="AE9:AF9"/>
+    <mergeCell ref="B46:AF47"/>
+    <mergeCell ref="AA33:AB33"/>
+    <mergeCell ref="AC33:AD33"/>
+    <mergeCell ref="AE33:AF33"/>
+    <mergeCell ref="B34:AF42"/>
+    <mergeCell ref="Y43:AE43"/>
+    <mergeCell ref="Y44:AE44"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="U33:V33"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="Y33:Z33"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="Z31:AF31"/>
+    <mergeCell ref="U32:V32"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="Y32:Z32"/>
+    <mergeCell ref="AA32:AB32"/>
+    <mergeCell ref="AC32:AD32"/>
+    <mergeCell ref="AE32:AF32"/>
+    <mergeCell ref="C29:AF29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:K30"/>
+    <mergeCell ref="Z30:AB30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="I31:K31"/>
+    <mergeCell ref="L31:Q31"/>
+    <mergeCell ref="S31:W31"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="B27:P27"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="T27:AD27"/>
+    <mergeCell ref="AE27:AF27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:L28"/>
+    <mergeCell ref="M28:P28"/>
+    <mergeCell ref="Q28:X28"/>
+    <mergeCell ref="Y28:AA28"/>
+    <mergeCell ref="AB28:AF28"/>
+    <mergeCell ref="B25:S25"/>
+    <mergeCell ref="T25:Y25"/>
+    <mergeCell ref="Z25:AD25"/>
+    <mergeCell ref="AE25:AF25"/>
+    <mergeCell ref="B26:S26"/>
+    <mergeCell ref="T26:AD26"/>
+    <mergeCell ref="AE26:AF26"/>
+    <mergeCell ref="AE23:AF23"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="K24:M24"/>
+    <mergeCell ref="N24:P24"/>
+    <mergeCell ref="Q24:S24"/>
+    <mergeCell ref="T24:Y24"/>
+    <mergeCell ref="Z24:AD24"/>
+    <mergeCell ref="AE24:AF24"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="K23:M23"/>
+    <mergeCell ref="N23:P23"/>
+    <mergeCell ref="Q23:S23"/>
+    <mergeCell ref="T23:Y23"/>
+    <mergeCell ref="Z23:AD23"/>
+    <mergeCell ref="AE21:AF21"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="K22:M22"/>
+    <mergeCell ref="N22:P22"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="T22:Y22"/>
+    <mergeCell ref="Z22:AD22"/>
+    <mergeCell ref="AE22:AF22"/>
+    <mergeCell ref="D21:J21"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="N21:P21"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="T21:Y21"/>
+    <mergeCell ref="Z21:AD21"/>
+    <mergeCell ref="AE19:AF19"/>
+    <mergeCell ref="D20:J20"/>
+    <mergeCell ref="K20:M20"/>
+    <mergeCell ref="N20:P20"/>
+    <mergeCell ref="Q20:S20"/>
+    <mergeCell ref="T20:Y20"/>
+    <mergeCell ref="Z20:AD20"/>
+    <mergeCell ref="AE20:AF20"/>
+    <mergeCell ref="D19:J19"/>
+    <mergeCell ref="K19:M19"/>
+    <mergeCell ref="N19:P19"/>
+    <mergeCell ref="Q19:S19"/>
+    <mergeCell ref="T19:Y19"/>
+    <mergeCell ref="Z19:AD19"/>
+    <mergeCell ref="AE17:AF17"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="K18:M18"/>
+    <mergeCell ref="N18:P18"/>
+    <mergeCell ref="Q18:S18"/>
+    <mergeCell ref="T18:Y18"/>
+    <mergeCell ref="Z18:AD18"/>
+    <mergeCell ref="AE18:AF18"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="N17:P17"/>
+    <mergeCell ref="Q17:S17"/>
+    <mergeCell ref="T17:Y17"/>
+    <mergeCell ref="Z17:AD17"/>
+    <mergeCell ref="AE15:AF15"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="K16:M16"/>
+    <mergeCell ref="N16:P16"/>
+    <mergeCell ref="Q16:S16"/>
+    <mergeCell ref="T16:Y16"/>
+    <mergeCell ref="Z16:AD16"/>
+    <mergeCell ref="AE16:AF16"/>
+    <mergeCell ref="D15:J15"/>
+    <mergeCell ref="K15:M15"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="Q15:S15"/>
+    <mergeCell ref="T15:Y15"/>
+    <mergeCell ref="Z15:AD15"/>
+    <mergeCell ref="AE13:AF13"/>
+    <mergeCell ref="D14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="Q14:S14"/>
+    <mergeCell ref="T14:Y14"/>
+    <mergeCell ref="Z14:AD14"/>
+    <mergeCell ref="AE14:AF14"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="K13:M13"/>
+    <mergeCell ref="N13:P13"/>
+    <mergeCell ref="Q13:S13"/>
+    <mergeCell ref="T13:Y13"/>
+    <mergeCell ref="Z13:AD13"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="K10:M10"/>
     <mergeCell ref="N10:P10"/>
@@ -3854,143 +3924,37 @@
     <mergeCell ref="Q11:S11"/>
     <mergeCell ref="T11:Y11"/>
     <mergeCell ref="Z11:AD11"/>
-    <mergeCell ref="AE13:AF13"/>
-    <mergeCell ref="D14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="N14:P14"/>
-    <mergeCell ref="Q14:S14"/>
-    <mergeCell ref="T14:Y14"/>
-    <mergeCell ref="Z14:AD14"/>
-    <mergeCell ref="AE14:AF14"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="K13:M13"/>
-    <mergeCell ref="N13:P13"/>
-    <mergeCell ref="Q13:S13"/>
-    <mergeCell ref="T13:Y13"/>
-    <mergeCell ref="Z13:AD13"/>
-    <mergeCell ref="AE15:AF15"/>
-    <mergeCell ref="D16:J16"/>
-    <mergeCell ref="K16:M16"/>
-    <mergeCell ref="N16:P16"/>
-    <mergeCell ref="Q16:S16"/>
-    <mergeCell ref="T16:Y16"/>
-    <mergeCell ref="Z16:AD16"/>
-    <mergeCell ref="AE16:AF16"/>
-    <mergeCell ref="D15:J15"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="N15:P15"/>
-    <mergeCell ref="Q15:S15"/>
-    <mergeCell ref="T15:Y15"/>
-    <mergeCell ref="Z15:AD15"/>
-    <mergeCell ref="AE17:AF17"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="N18:P18"/>
-    <mergeCell ref="Q18:S18"/>
-    <mergeCell ref="T18:Y18"/>
-    <mergeCell ref="Z18:AD18"/>
-    <mergeCell ref="AE18:AF18"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="N17:P17"/>
-    <mergeCell ref="Q17:S17"/>
-    <mergeCell ref="T17:Y17"/>
-    <mergeCell ref="Z17:AD17"/>
-    <mergeCell ref="AE19:AF19"/>
-    <mergeCell ref="D20:J20"/>
-    <mergeCell ref="K20:M20"/>
-    <mergeCell ref="N20:P20"/>
-    <mergeCell ref="Q20:S20"/>
-    <mergeCell ref="T20:Y20"/>
-    <mergeCell ref="Z20:AD20"/>
-    <mergeCell ref="AE20:AF20"/>
-    <mergeCell ref="D19:J19"/>
-    <mergeCell ref="K19:M19"/>
-    <mergeCell ref="N19:P19"/>
-    <mergeCell ref="Q19:S19"/>
-    <mergeCell ref="T19:Y19"/>
-    <mergeCell ref="Z19:AD19"/>
-    <mergeCell ref="AE21:AF21"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="K22:M22"/>
-    <mergeCell ref="N22:P22"/>
-    <mergeCell ref="Q22:S22"/>
-    <mergeCell ref="T22:Y22"/>
-    <mergeCell ref="Z22:AD22"/>
-    <mergeCell ref="AE22:AF22"/>
-    <mergeCell ref="D21:J21"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="N21:P21"/>
-    <mergeCell ref="Q21:S21"/>
-    <mergeCell ref="T21:Y21"/>
-    <mergeCell ref="Z21:AD21"/>
-    <mergeCell ref="B25:S25"/>
-    <mergeCell ref="T25:Y25"/>
-    <mergeCell ref="Z25:AD25"/>
-    <mergeCell ref="AE25:AF25"/>
-    <mergeCell ref="B26:S26"/>
-    <mergeCell ref="T26:AD26"/>
-    <mergeCell ref="AE26:AF26"/>
-    <mergeCell ref="AE23:AF23"/>
-    <mergeCell ref="D24:J24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="Q24:S24"/>
-    <mergeCell ref="T24:Y24"/>
-    <mergeCell ref="Z24:AD24"/>
-    <mergeCell ref="AE24:AF24"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="K23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="Q23:S23"/>
-    <mergeCell ref="T23:Y23"/>
-    <mergeCell ref="Z23:AD23"/>
-    <mergeCell ref="B27:P27"/>
-    <mergeCell ref="Q27:S27"/>
-    <mergeCell ref="T27:AD27"/>
-    <mergeCell ref="AE27:AF27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:L28"/>
-    <mergeCell ref="M28:P28"/>
-    <mergeCell ref="Q28:X28"/>
-    <mergeCell ref="Y28:AA28"/>
-    <mergeCell ref="AB28:AF28"/>
-    <mergeCell ref="Z31:AF31"/>
-    <mergeCell ref="U32:V32"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="Y32:Z32"/>
-    <mergeCell ref="AA32:AB32"/>
-    <mergeCell ref="AC32:AD32"/>
-    <mergeCell ref="AE32:AF32"/>
-    <mergeCell ref="C29:AF29"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:K30"/>
-    <mergeCell ref="Z30:AB30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:K31"/>
-    <mergeCell ref="L31:Q31"/>
-    <mergeCell ref="S31:W31"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="B46:AF47"/>
-    <mergeCell ref="AA33:AB33"/>
-    <mergeCell ref="AC33:AD33"/>
-    <mergeCell ref="AE33:AF33"/>
-    <mergeCell ref="B34:AF42"/>
-    <mergeCell ref="Y43:AE43"/>
-    <mergeCell ref="Y44:AE44"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="U33:V33"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="Y33:Z33"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="G7:AD7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="G8:P8"/>
+    <mergeCell ref="T8:AE8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="T9:Y9"/>
+    <mergeCell ref="Z9:AD9"/>
+    <mergeCell ref="AE9:AF9"/>
+    <mergeCell ref="B2:AF2"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="K3:K6"/>
+    <mergeCell ref="L3:O3"/>
+    <mergeCell ref="P3:AF3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="P4:W4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AF4"/>
+    <mergeCell ref="B5:J5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="P5:AF5"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="P6:U6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="X6:AF6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
